--- a/tasks_gradebook.xlsx
+++ b/tasks_gradebook.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00B7E4C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCD5"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -128,19 +133,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -670,7 +678,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>96.2</v>
+        <v>82.8</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -683,7 +691,7 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -696,7 +704,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>86.5</v>
+        <v>75.8</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -709,7 +717,7 @@
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>94.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -722,7 +730,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
@@ -735,17 +743,17 @@
         </is>
       </c>
       <c r="S2" s="3" t="n">
-        <v>467</v>
+        <v>413.4</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>82.7</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
@@ -771,7 +779,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>63.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -784,7 +792,7 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>71</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -797,7 +805,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>68.2</v>
+        <v>88.2</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -810,7 +818,7 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>74.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
@@ -823,7 +831,7 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
@@ -836,17 +844,17 @@
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>348.7</v>
+        <v>448.4</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>89.7</v>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
@@ -872,7 +880,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>82.5</v>
+        <v>81.8</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -885,7 +893,7 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>85.8</v>
+        <v>87</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -898,7 +906,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>69.7</v>
+        <v>72.7</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -911,7 +919,7 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>79.3</v>
+        <v>84.3</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -924,7 +932,7 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>78.7</v>
+        <v>85.5</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
@@ -937,17 +945,17 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>396</v>
+        <v>411.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>79.2</v>
+        <v>82.3</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -973,7 +981,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>57.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -986,7 +994,7 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>63.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -999,7 +1007,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
@@ -1012,7 +1020,7 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>64.7</v>
+        <v>69</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
@@ -1025,7 +1033,7 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>82.2</v>
+        <v>85.3</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -1038,17 +1046,17 @@
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>348.8</v>
+        <v>376.8</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>69.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
@@ -1074,7 +1082,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>59.7</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -1087,7 +1095,7 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>72.2</v>
+        <v>57.1</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -1100,7 +1108,7 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>78</v>
+        <v>62.3</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -1113,7 +1121,7 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1134,7 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>85.8</v>
+        <v>69.2</v>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
@@ -1139,17 +1147,17 @@
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>378.8</v>
+        <v>300.6</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>75.8</v>
+        <v>60.1</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
@@ -1175,7 +1183,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>81.3</v>
+        <v>69.7</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -1188,7 +1196,7 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>75.2</v>
+        <v>63.3</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1201,7 +1209,7 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>77.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -1214,7 +1222,7 @@
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>90.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
@@ -1227,7 +1235,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
@@ -1240,17 +1248,17 @@
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>409.9</v>
+        <v>349.2</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>82</v>
+        <v>69.8</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1276,7 +1284,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>69.8</v>
+        <v>56.7</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -1289,7 +1297,7 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>72.5</v>
+        <v>59.5</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1302,21 +1310,21 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-18 13:30</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>75.8</v>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-18 13:30</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>88.7</v>
-      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>2026-03-02 09:59</t>
@@ -1328,7 +1336,7 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>87.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1341,17 +1349,17 @@
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>394.3</v>
+        <v>329.5</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -1377,7 +1385,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>75.5</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -1390,7 +1398,7 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>55.8</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -1403,7 +1411,7 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -1416,7 +1424,7 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82</v>
+        <v>69.7</v>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
@@ -1429,7 +1437,7 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>76.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
@@ -1442,17 +1450,17 @@
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>379.1</v>
+        <v>315.6</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>75.8</v>
+        <v>63.1</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
@@ -1478,7 +1486,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>75.8</v>
+        <v>65.7</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -1491,7 +1499,7 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>69.3</v>
+        <v>59.8</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -1504,7 +1512,7 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>74.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -1517,7 +1525,7 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>76.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1530,7 +1538,7 @@
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>72.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
@@ -1543,17 +1551,17 @@
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>368.3</v>
+        <v>322.9</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>73.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -1579,7 +1587,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -1592,7 +1600,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>66.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -1605,7 +1613,7 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>72.2</v>
+        <v>72.8</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -1618,7 +1626,7 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1639,7 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
@@ -1644,13 +1652,13 @@
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -1680,7 +1688,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>69.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -1693,7 +1701,7 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>65.5</v>
+        <v>64.7</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1714,7 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>65.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
@@ -1719,7 +1727,7 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>70.2</v>
+        <v>71.8</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1732,7 +1740,7 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>59.7</v>
+        <v>62.4</v>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
@@ -1745,13 +1753,13 @@
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>329.9</v>
+        <v>331.9</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -1781,7 +1789,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>70.3</v>
+        <v>44.7</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -1794,7 +1802,7 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>73.7</v>
+        <v>47.4</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -1807,7 +1815,7 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>78.8</v>
+        <v>51.7</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -1820,7 +1828,7 @@
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
@@ -1833,7 +1841,7 @@
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>84.5</v>
+        <v>55.8</v>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -1846,17 +1854,17 @@
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>399.7</v>
+        <v>264.1</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>52.8</v>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
@@ -1882,7 +1890,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>66.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1903,7 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>81.2</v>
+        <v>92.7</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -1908,7 +1916,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -1921,7 +1929,7 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1934,7 +1942,7 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
@@ -1947,17 +1955,17 @@
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>362.5</v>
+        <v>415.6</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>72.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
@@ -1983,7 +1991,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>62</v>
+        <v>53.1</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -1996,7 +2004,7 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>57.9</v>
+        <v>49.2</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2017,7 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>64.7</v>
+        <v>56.2</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -2022,7 +2030,7 @@
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
@@ -2035,7 +2043,7 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>57.4</v>
+        <v>49.2</v>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
@@ -2048,17 +2056,17 @@
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>318.1</v>
+        <v>275.4</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>63.6</v>
+        <v>55.1</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
@@ -2084,7 +2092,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>76.2</v>
+        <v>70.7</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -2097,7 +2105,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>77.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -2110,7 +2118,7 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>74.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
@@ -2123,7 +2131,7 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2136,7 +2144,7 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
@@ -2149,17 +2157,17 @@
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>384.8</v>
+        <v>349.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>77</v>
+        <v>69.8</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
@@ -2185,7 +2193,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -2198,7 +2206,7 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>60.1</v>
+        <v>60.3</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -2211,7 +2219,7 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -2224,7 +2232,7 @@
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
@@ -2237,7 +2245,7 @@
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
@@ -2250,13 +2258,13 @@
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>309.9</v>
+        <v>309.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -2286,7 +2294,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -2299,7 +2307,7 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -2312,7 +2320,7 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>85.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -2325,7 +2333,7 @@
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>95.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2338,7 +2346,7 @@
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
@@ -2351,17 +2359,17 @@
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>431.2</v>
+        <v>386.8</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2387,7 +2395,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>74.2</v>
+        <v>78.8</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -2400,7 +2408,7 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -2413,7 +2421,7 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -2426,7 +2434,7 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
@@ -2439,7 +2447,7 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
@@ -2452,13 +2460,13 @@
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>375.4</v>
+        <v>398.6</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -2488,7 +2496,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>70</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -2501,7 +2509,7 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -2514,7 +2522,7 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>84.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
@@ -2527,7 +2535,7 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>80.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
@@ -2540,7 +2548,7 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>73.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
@@ -2553,17 +2561,17 @@
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>373.4</v>
+        <v>437.3</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>87.5</v>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
@@ -2589,7 +2597,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -2602,7 +2610,7 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -2615,7 +2623,7 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -2628,7 +2636,7 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
@@ -2654,17 +2662,17 @@
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>447.4</v>
+        <v>416.3</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>83.3</v>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
@@ -2674,23 +2682,23 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>STD-021</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>فاطمة علي</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -2703,7 +2711,7 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -2716,7 +2724,7 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>66.7</v>
+        <v>55.4</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
@@ -2729,7 +2737,7 @@
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2742,7 +2750,7 @@
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
@@ -2755,17 +2763,17 @@
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>392.6</v>
+        <v>336.3</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>78.5</v>
+        <v>67.3</v>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -2775,23 +2783,23 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>STD-022</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>زينب عبدالله</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -2804,7 +2812,7 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -2817,7 +2825,7 @@
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -2830,7 +2838,7 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
@@ -2843,7 +2851,7 @@
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
@@ -2856,17 +2864,17 @@
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>388.1</v>
+        <v>349.6</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -2876,23 +2884,23 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>STD-023</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>هبة الله ماجد</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>80.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -2905,7 +2913,7 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -2918,7 +2926,7 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>71.3</v>
+        <v>73.5</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
@@ -2931,7 +2939,7 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2944,7 +2952,7 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
@@ -2957,17 +2965,17 @@
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>396.4</v>
+        <v>407.2</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>79.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -2977,23 +2985,23 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>STD-024</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>ندى رمضان</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -3006,7 +3014,7 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>67.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -3019,7 +3027,7 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -3032,7 +3040,7 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>63.6</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
@@ -3045,7 +3053,7 @@
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>58.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
@@ -3058,17 +3066,17 @@
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>344.8</v>
+        <v>384.4</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>69</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3078,98 +3086,98 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>STD-025</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>روان كمال</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>2026-01-25 21:17</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="G26" s="7" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>2026-02-10 18:35</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="J26" s="6" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
+      <c r="J26" s="7" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>2026-02-24 14:23</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="M26" s="6" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="N26" s="6" t="inlineStr">
+      <c r="M26" s="7" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>2026-03-12 09:16</t>
         </is>
       </c>
-      <c r="O26" s="6" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="P26" s="6" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="P26" s="7" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>2026-03-25 16:53</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>337.8</v>
+        <v>278.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -3179,23 +3187,23 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>STD-026</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>جنى هشام</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>80.2</v>
+        <v>77.3</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -3208,7 +3216,7 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>81.7</v>
+        <v>79.7</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -3221,7 +3229,7 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>77.3</v>
+        <v>76.3</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -3234,7 +3242,7 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
@@ -3247,7 +3255,7 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>80</v>
+        <v>80.8</v>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
@@ -3260,13 +3268,13 @@
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>405.9</v>
+        <v>400.7</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>81.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
@@ -3280,23 +3288,23 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>STD-027</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>بسمة نبيل</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -3309,7 +3317,7 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>55.2</v>
+        <v>71.5</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -3322,7 +3330,7 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>68.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
@@ -3335,7 +3343,7 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>81.2</v>
+        <v>96.3</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3348,7 +3356,7 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
@@ -3361,17 +3369,17 @@
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>330.1</v>
+        <v>408.8</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>66</v>
+        <v>81.8</v>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -3381,23 +3389,23 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>STD-028</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>ملك أيمن</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -3410,7 +3418,7 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -3423,7 +3431,7 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>74.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
@@ -3436,7 +3444,7 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
@@ -3449,7 +3457,7 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
@@ -3462,17 +3470,17 @@
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>331.9</v>
+        <v>314.9</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
@@ -3482,98 +3490,98 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>STD-029</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>تقى شريف</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="D30" s="7" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>2026-01-26 17:52</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="G30" s="7" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>2026-02-11 13:26</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="J30" s="6" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
+      <c r="J30" s="7" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>2026-02-25 14:53</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="M30" s="6" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
+      <c r="M30" s="7" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>2026-03-12 22:57</t>
         </is>
       </c>
-      <c r="O30" s="6" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="P30" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="P30" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>2026-03-23 19:30</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>380.9</v>
+        <v>343</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>76.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -3583,23 +3591,23 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>STD-030</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>لجين سمير</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>69.5</v>
+        <v>84.3</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -3612,7 +3620,7 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>56</v>
+        <v>71.7</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -3625,7 +3633,7 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>56</v>
+        <v>72.7</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -3638,7 +3646,7 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>72.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
@@ -3651,7 +3659,7 @@
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>53.6</v>
+        <v>72.3</v>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
@@ -3664,17 +3672,17 @@
         </is>
       </c>
       <c r="S31" s="3" t="n">
-        <v>307.6</v>
+        <v>391.1</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>61.5</v>
+        <v>78.2</v>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -3684,23 +3692,23 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>STD-031</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>ياسمين وائل</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -3713,7 +3721,7 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -3726,7 +3734,7 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -3739,7 +3747,7 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>81.7</v>
+        <v>79.5</v>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
@@ -3752,7 +3760,7 @@
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>81.7</v>
+        <v>79.2</v>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
@@ -3765,13 +3773,13 @@
         </is>
       </c>
       <c r="S32" s="3" t="n">
-        <v>396.1</v>
+        <v>386.3</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>79.2</v>
+        <v>77.3</v>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
@@ -3785,23 +3793,23 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>STD-032</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>حبيبة عصام</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>63.6</v>
+        <v>62.9</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -3814,7 +3822,7 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>75</v>
+        <v>73.2</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -3827,7 +3835,7 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>67.3</v>
+        <v>64.5</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -3840,7 +3848,7 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>74.5</v>
+        <v>70.7</v>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
@@ -3853,7 +3861,7 @@
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>55.8</v>
+        <v>50.9</v>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
@@ -3866,17 +3874,17 @@
         </is>
       </c>
       <c r="S33" s="3" t="n">
-        <v>336.2</v>
+        <v>322.2</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>67.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -3886,23 +3894,23 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>STD-033</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>مها رضا</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>59.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -3915,7 +3923,7 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>54.8</v>
+        <v>82</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -3928,7 +3936,7 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>53.2</v>
+        <v>79.8</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -3941,7 +3949,7 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>57.4</v>
+        <v>83.3</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3954,7 +3962,7 @@
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>63.2</v>
+        <v>88.5</v>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
@@ -3967,17 +3975,17 @@
         </is>
       </c>
       <c r="S34" s="3" t="n">
-        <v>288.3</v>
+        <v>421.2</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>57.7</v>
+        <v>84.2</v>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
@@ -3987,23 +3995,23 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>STD-034</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>داليا منير</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>78.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -4016,7 +4024,7 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>61.6</v>
+        <v>75.8</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -4029,7 +4037,7 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -4042,7 +4050,7 @@
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>69.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
@@ -4055,7 +4063,7 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
@@ -4068,17 +4076,17 @@
         </is>
       </c>
       <c r="S35" s="3" t="n">
-        <v>354.8</v>
+        <v>431.4</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>86.3</v>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
@@ -4088,23 +4096,23 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>STD-035</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>سمر حسام</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>86.8</v>
+        <v>92.5</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -4117,7 +4125,7 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>83.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -4130,7 +4138,7 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>90.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -4143,7 +4151,7 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
@@ -4156,7 +4164,7 @@
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
@@ -4169,17 +4177,17 @@
         </is>
       </c>
       <c r="S36" s="3" t="n">
-        <v>416.2</v>
+        <v>461.9</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
@@ -4189,23 +4197,23 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>STD-036</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>نور عماد</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>65.8</v>
+        <v>52.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -4218,7 +4226,7 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>72.5</v>
+        <v>58.5</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -4231,7 +4239,7 @@
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>75</v>
+        <v>59.9</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -4244,7 +4252,7 @@
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>68</v>
+        <v>51.7</v>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
@@ -4257,7 +4265,7 @@
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
@@ -4270,17 +4278,17 @@
         </is>
       </c>
       <c r="S37" s="3" t="n">
-        <v>361.7</v>
+        <v>285.9</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>72.3</v>
+        <v>57.2</v>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -4290,23 +4298,23 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>STD-037</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>إيمان بدر</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>86.5</v>
+        <v>71.2</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -4319,7 +4327,7 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>100</v>
+        <v>91.3</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -4332,7 +4340,7 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -4345,7 +4353,7 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>79.5</v>
+        <v>68</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -4358,7 +4366,7 @@
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
@@ -4371,17 +4379,17 @@
         </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>450.6</v>
+        <v>392.9</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="V38" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>78.59999999999999</v>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
@@ -4391,98 +4399,98 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>STD-038</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>هند صلاح</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="D39" s="7" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>2026-01-28 20:31</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G39" s="6" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="G39" s="7" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>2026-02-11 11:13</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="J39" s="6" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="K39" s="6" t="inlineStr">
+      <c r="J39" s="7" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>2026-02-23 12:35</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="M39" s="6" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="M39" s="7" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>2026-03-12 11:54</t>
         </is>
       </c>
-      <c r="O39" s="6" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="P39" s="6" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="P39" s="7" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
         <is>
           <t>2026-03-23 15:51</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="S39" s="3" t="n">
-        <v>287.8</v>
+        <v>317.2</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>57.6</v>
+        <v>63.4</v>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -4492,23 +4500,23 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>STD-039</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>ميرنا جابر</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>57.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -4521,7 +4529,7 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>62.9</v>
+        <v>73.2</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
@@ -4534,7 +4542,7 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>61.5</v>
+        <v>72.3</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4555,7 @@
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>69.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -4560,7 +4568,7 @@
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>57.3</v>
+        <v>69</v>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
@@ -4573,17 +4581,17 @@
         </is>
       </c>
       <c r="S40" s="3" t="n">
-        <v>308.1</v>
+        <v>362</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>61.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
@@ -4593,23 +4601,23 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>STD-040</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>كريمة ناصر</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>55.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -4622,7 +4630,7 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>86.3</v>
+        <v>100</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -4635,7 +4643,7 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>60.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -4648,7 +4656,7 @@
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
@@ -4661,7 +4669,7 @@
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
@@ -4674,17 +4682,17 @@
         </is>
       </c>
       <c r="S41" s="3" t="n">
-        <v>356.3</v>
+        <v>431.3</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>86.3</v>
+      </c>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -4694,23 +4702,23 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>STD-041</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>ياسمين خالد</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>70.7</v>
+        <v>96</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -4723,7 +4731,7 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>59.9</v>
+        <v>86.5</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -4736,7 +4744,7 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>65.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -4749,7 +4757,7 @@
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>70.8</v>
+        <v>93.5</v>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
@@ -4762,7 +4770,7 @@
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
@@ -4775,17 +4783,17 @@
         </is>
       </c>
       <c r="S42" s="3" t="n">
-        <v>345.8</v>
+        <v>463.6</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>92.7</v>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
@@ -4795,23 +4803,23 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>STD-042</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>هاجر عبدالعزيز</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>63.8</v>
+        <v>72.5</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -4824,7 +4832,7 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>69.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -4837,7 +4845,7 @@
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -4850,7 +4858,7 @@
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>77.3</v>
+        <v>84.8</v>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
@@ -4863,7 +4871,7 @@
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
@@ -4876,17 +4884,17 @@
         </is>
       </c>
       <c r="S43" s="3" t="n">
-        <v>363.9</v>
+        <v>403.3</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>72.8</v>
+        <v>80.7</v>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
@@ -4896,23 +4904,23 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>STD-043</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>رحمة طه</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4933,7 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -4938,7 +4946,7 @@
         </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>83.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -4951,7 +4959,7 @@
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>86.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4964,7 +4972,7 @@
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>91.5</v>
+        <v>89</v>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
@@ -4977,13 +4985,13 @@
         </is>
       </c>
       <c r="S44" s="3" t="n">
-        <v>417.3</v>
+        <v>413.7</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>83.5</v>
+        <v>82.7</v>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
@@ -4997,23 +5005,23 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>STD-044</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>أمل فاروق</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -5026,7 +5034,7 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>75.8</v>
+        <v>63.8</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -5039,7 +5047,7 @@
         </is>
       </c>
       <c r="J45" s="3" t="n">
-        <v>79.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -5052,7 +5060,7 @@
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>78.8</v>
+        <v>68.2</v>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
@@ -5065,7 +5073,7 @@
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
@@ -5078,17 +5086,17 @@
         </is>
       </c>
       <c r="S45" s="3" t="n">
-        <v>386.4</v>
+        <v>329.8</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>77.3</v>
+        <v>66</v>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
@@ -5098,23 +5106,23 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>STD-045</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>سهام عبدالحميد</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>64.5</v>
+        <v>89.5</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -5127,7 +5135,7 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>65.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
@@ -5140,7 +5148,7 @@
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
@@ -5153,7 +5161,7 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>69.2</v>
+        <v>93.3</v>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
@@ -5166,7 +5174,7 @@
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>69.5</v>
+        <v>93.3</v>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
@@ -5179,17 +5187,17 @@
         </is>
       </c>
       <c r="S46" s="3" t="n">
-        <v>333.3</v>
+        <v>455.4</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>91.09999999999999</v>
+      </c>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
@@ -5199,23 +5207,23 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>STD-046</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>وفاء محسن</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>87.7</v>
+        <v>77.8</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -5228,7 +5236,7 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -5241,7 +5249,7 @@
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
@@ -5254,7 +5262,7 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>84.2</v>
+        <v>79</v>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
@@ -5267,7 +5275,7 @@
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>85.5</v>
+        <v>81.8</v>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
@@ -5280,17 +5288,17 @@
         </is>
       </c>
       <c r="S47" s="3" t="n">
-        <v>431.6</v>
+        <v>397.7</v>
       </c>
       <c r="T47" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="V47" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>79.5</v>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="W47" s="3" t="inlineStr">
@@ -5300,23 +5308,23 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>STD-047</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>ثريا كرم</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -5329,7 +5337,7 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>66.5</v>
+        <v>72.7</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
@@ -5342,7 +5350,7 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>70.8</v>
+        <v>76.2</v>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
@@ -5355,7 +5363,7 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>66.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
@@ -5368,7 +5376,7 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
@@ -5381,17 +5389,17 @@
         </is>
       </c>
       <c r="S48" s="3" t="n">
-        <v>349.9</v>
+        <v>377</v>
       </c>
       <c r="T48" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>70</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="V48" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W48" s="3" t="inlineStr">
@@ -5401,23 +5409,23 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>STD-048</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>نسمة أنور</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -5443,7 +5451,7 @@
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>78.2</v>
+        <v>79.3</v>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
@@ -5456,7 +5464,7 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>82.3</v>
+        <v>84.5</v>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
@@ -5469,7 +5477,7 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
@@ -5482,17 +5490,17 @@
         </is>
       </c>
       <c r="S49" s="3" t="n">
-        <v>396.4</v>
+        <v>401.9</v>
       </c>
       <c r="T49" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>79.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="V49" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W49" s="3" t="inlineStr">
@@ -5502,23 +5510,23 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>STD-049</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>جيهان فوزي</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -5531,7 +5539,7 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>77.2</v>
+        <v>77.7</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
@@ -5544,7 +5552,7 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
@@ -5557,7 +5565,7 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -5570,7 +5578,7 @@
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>90.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
@@ -5583,13 +5591,13 @@
         </is>
       </c>
       <c r="S50" s="3" t="n">
-        <v>403.4</v>
+        <v>399.9</v>
       </c>
       <c r="T50" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>80.7</v>
+        <v>80</v>
       </c>
       <c r="V50" s="3" t="inlineStr">
         <is>
@@ -5603,23 +5611,23 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>STD-050</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>عزة سيد</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>71</v>
+        <v>61.8</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -5632,7 +5640,7 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -5645,7 +5653,7 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
@@ -5658,7 +5666,7 @@
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
@@ -5671,7 +5679,7 @@
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
@@ -5684,17 +5692,17 @@
         </is>
       </c>
       <c r="S51" s="3" t="n">
-        <v>411.2</v>
+        <v>360.6</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>82.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="V51" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W51" s="3" t="inlineStr">
@@ -5704,23 +5712,23 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>STD-051</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>سحر عبدالفتاح</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>74.2</v>
+        <v>72</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -5733,7 +5741,7 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
@@ -5746,7 +5754,7 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>91.2</v>
+        <v>88.5</v>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
@@ -5759,7 +5767,7 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -5772,7 +5780,7 @@
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>93.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
@@ -5785,17 +5793,17 @@
         </is>
       </c>
       <c r="S52" s="3" t="n">
-        <v>425.6</v>
+        <v>412</v>
       </c>
       <c r="T52" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="V52" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>82.40000000000001</v>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="W52" s="3" t="inlineStr">
@@ -5805,23 +5813,23 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>STD-052</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>إنجي حازم</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -5834,7 +5842,7 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
@@ -5847,7 +5855,7 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>77</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
@@ -5860,7 +5868,7 @@
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
@@ -5873,7 +5881,7 @@
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
@@ -5886,17 +5894,17 @@
         </is>
       </c>
       <c r="S53" s="3" t="n">
-        <v>401.6</v>
+        <v>395.8</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>80.3</v>
+        <v>79.2</v>
       </c>
       <c r="V53" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W53" s="3" t="inlineStr">
@@ -5906,23 +5914,23 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>STD-053</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>مروة شوقي</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -5935,7 +5943,7 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>80.8</v>
+        <v>82.2</v>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
@@ -5948,7 +5956,7 @@
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
@@ -5961,7 +5969,7 @@
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>80.7</v>
+        <v>83.2</v>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
@@ -5974,7 +5982,7 @@
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>87.7</v>
+        <v>90.8</v>
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
@@ -5987,13 +5995,13 @@
         </is>
       </c>
       <c r="S54" s="3" t="n">
-        <v>404.8</v>
+        <v>414.6</v>
       </c>
       <c r="T54" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>81</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V54" s="3" t="inlineStr">
         <is>
@@ -6007,23 +6015,23 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>STD-054</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>غادة رفعت</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>85.5</v>
+        <v>61.4</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -6036,7 +6044,7 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -6049,7 +6057,7 @@
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>88.3</v>
+        <v>63.2</v>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
@@ -6062,7 +6070,7 @@
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
@@ -6075,7 +6083,7 @@
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>92.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
@@ -6088,17 +6096,17 @@
         </is>
       </c>
       <c r="S55" s="3" t="n">
-        <v>448</v>
+        <v>322.5</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="V55" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>64.5</v>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>D+</t>
         </is>
       </c>
       <c r="W55" s="3" t="inlineStr">
@@ -6108,23 +6116,23 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>STD-055</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>صفاء عاطف</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -6137,7 +6145,7 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>67</v>
+        <v>63.7</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
@@ -6150,7 +6158,7 @@
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
@@ -6163,7 +6171,7 @@
         </is>
       </c>
       <c r="M56" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -6176,7 +6184,7 @@
         </is>
       </c>
       <c r="P56" s="3" t="n">
-        <v>82.5</v>
+        <v>78</v>
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
@@ -6189,13 +6197,13 @@
         </is>
       </c>
       <c r="S56" s="3" t="n">
-        <v>372.6</v>
+        <v>353.8</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>74.5</v>
+        <v>70.8</v>
       </c>
       <c r="V56" s="3" t="inlineStr">
         <is>
@@ -6209,23 +6217,23 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>STD-056</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>هالة مجدي</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>77.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -6238,7 +6246,7 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -6251,7 +6259,7 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
@@ -6264,7 +6272,7 @@
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>77.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
@@ -6277,7 +6285,7 @@
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
@@ -6290,17 +6298,17 @@
         </is>
       </c>
       <c r="S57" s="3" t="n">
-        <v>406.5</v>
+        <v>428.9</v>
       </c>
       <c r="T57" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="V57" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>85.8</v>
+      </c>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="W57" s="3" t="inlineStr">
@@ -6310,23 +6318,23 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>STD-057</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>لبنى حمدان</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>77.2</v>
+        <v>64</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -6339,7 +6347,7 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>81</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
@@ -6352,7 +6360,7 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>89.3</v>
+        <v>76.8</v>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
@@ -6365,7 +6373,7 @@
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>87.7</v>
+        <v>75.5</v>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
@@ -6378,7 +6386,7 @@
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>85</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
@@ -6391,17 +6399,17 @@
         </is>
       </c>
       <c r="S58" s="3" t="n">
-        <v>420.2</v>
+        <v>357.5</v>
       </c>
       <c r="T58" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>84</v>
+        <v>71.5</v>
       </c>
       <c r="V58" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W58" s="3" t="inlineStr">
@@ -6411,23 +6419,23 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>STD-058</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>رانيا شعبان</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -6440,7 +6448,7 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -6453,7 +6461,7 @@
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>69.5</v>
+        <v>68.2</v>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
@@ -6466,7 +6474,7 @@
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>74.2</v>
+        <v>71.5</v>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
@@ -6479,7 +6487,7 @@
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
@@ -6492,13 +6500,13 @@
         </is>
       </c>
       <c r="S59" s="3" t="n">
-        <v>359.9</v>
+        <v>353.4</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>72</v>
+        <v>70.7</v>
       </c>
       <c r="V59" s="3" t="inlineStr">
         <is>
@@ -6512,23 +6520,23 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>STD-059</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>سوزان هاني</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>72.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -6541,7 +6549,7 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>73</v>
+        <v>70.3</v>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
@@ -6554,7 +6562,7 @@
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
@@ -6567,7 +6575,7 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
@@ -6580,7 +6588,7 @@
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
@@ -6593,13 +6601,13 @@
         </is>
       </c>
       <c r="S60" s="3" t="n">
-        <v>366.8</v>
+        <v>355</v>
       </c>
       <c r="T60" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="V60" s="3" t="inlineStr">
         <is>
@@ -6613,23 +6621,23 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>STD-060</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>نيفين بهاء</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -6642,7 +6650,7 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>72.7</v>
+        <v>80.8</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
@@ -6655,7 +6663,7 @@
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>63.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
@@ -6668,7 +6676,7 @@
         </is>
       </c>
       <c r="M61" s="3" t="n">
-        <v>71.8</v>
+        <v>80</v>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
@@ -6681,7 +6689,7 @@
         </is>
       </c>
       <c r="P61" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
@@ -6694,17 +6702,17 @@
         </is>
       </c>
       <c r="S61" s="3" t="n">
-        <v>352.7</v>
+        <v>393.3</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>70.5</v>
+        <v>78.7</v>
       </c>
       <c r="V61" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W61" s="3" t="inlineStr">
@@ -6714,23 +6722,23 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>STD-061</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>هاجر عبدالله</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>55.6</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -6743,7 +6751,7 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>68.5</v>
+        <v>89.7</v>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
@@ -6756,7 +6764,7 @@
         </is>
       </c>
       <c r="J62" s="3" t="n">
-        <v>67</v>
+        <v>87.7</v>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
@@ -6769,7 +6777,7 @@
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
@@ -6782,7 +6790,7 @@
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>68.7</v>
+        <v>88.7</v>
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
@@ -6795,17 +6803,17 @@
         </is>
       </c>
       <c r="S62" s="3" t="n">
-        <v>330.7</v>
+        <v>434.5</v>
       </c>
       <c r="T62" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="V62" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>86.90000000000001</v>
+      </c>
+      <c r="V62" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="W62" s="3" t="inlineStr">
@@ -6815,23 +6823,23 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>STD-062</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>جومانا عادل</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>79.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -6844,7 +6852,7 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>81.7</v>
+        <v>71.7</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -6857,7 +6865,7 @@
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>79.8</v>
+        <v>71.2</v>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
@@ -6870,7 +6878,7 @@
         </is>
       </c>
       <c r="M63" s="3" t="n">
-        <v>80.8</v>
+        <v>73.8</v>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
@@ -6883,7 +6891,7 @@
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>82.3</v>
+        <v>76.7</v>
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
@@ -6896,17 +6904,17 @@
         </is>
       </c>
       <c r="S63" s="3" t="n">
-        <v>404.3</v>
+        <v>361.5</v>
       </c>
       <c r="T63" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="V63" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W63" s="3" t="inlineStr">
@@ -6916,23 +6924,23 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>STD-063</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>رقية حسني</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>71.8</v>
+        <v>57.6</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -6945,7 +6953,7 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
@@ -6958,7 +6966,7 @@
         </is>
       </c>
       <c r="J64" s="3" t="n">
-        <v>79.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
@@ -6971,7 +6979,7 @@
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
@@ -6984,7 +6992,7 @@
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>88.5</v>
+        <v>73</v>
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
@@ -6997,17 +7005,17 @@
         </is>
       </c>
       <c r="S64" s="3" t="n">
-        <v>400.1</v>
+        <v>325.8</v>
       </c>
       <c r="T64" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>80</v>
+        <v>65.2</v>
       </c>
       <c r="V64" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W64" s="3" t="inlineStr">
@@ -7017,23 +7025,23 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>STD-064</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>ضحى عبدالناصر</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>61.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -7046,7 +7054,7 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>67</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -7059,7 +7067,7 @@
         </is>
       </c>
       <c r="J65" s="3" t="n">
-        <v>74.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
@@ -7072,7 +7080,7 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>69.7</v>
+        <v>74</v>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
@@ -7085,7 +7093,7 @@
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>72.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
@@ -7098,17 +7106,17 @@
         </is>
       </c>
       <c r="S65" s="3" t="n">
-        <v>344.9</v>
+        <v>369</v>
       </c>
       <c r="T65" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U65" s="3" t="n">
-        <v>69</v>
+        <v>73.8</v>
       </c>
       <c r="V65" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W65" s="3" t="inlineStr">
@@ -7118,23 +7126,23 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>STD-065</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>تسنيم فؤاد</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>79.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -7147,7 +7155,7 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>84.2</v>
+        <v>69.2</v>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
@@ -7160,7 +7168,7 @@
         </is>
       </c>
       <c r="J66" s="3" t="n">
-        <v>83.3</v>
+        <v>68.2</v>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
@@ -7173,7 +7181,7 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
@@ -7186,7 +7194,7 @@
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>90.7</v>
+        <v>75.3</v>
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
@@ -7199,17 +7207,17 @@
         </is>
       </c>
       <c r="S66" s="3" t="n">
-        <v>427.8</v>
+        <v>352.2</v>
       </c>
       <c r="T66" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="V66" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>C+</t>
         </is>
       </c>
       <c r="W66" s="3" t="inlineStr">
@@ -7219,98 +7227,98 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>STD-066</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>أروى مدحت</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="D67" s="7" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>2026-01-27 12:31</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G67" s="6" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="G67" s="7" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>2026-02-09 12:29</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="J67" s="6" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="K67" s="6" t="inlineStr">
+      <c r="J67" s="7" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>2026-02-26 14:31</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="M67" s="6" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="M67" s="7" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>2026-03-10 13:32</t>
         </is>
       </c>
-      <c r="O67" s="6" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="P67" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q67" s="6" t="inlineStr">
+      <c r="P67" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q67" s="7" t="inlineStr">
         <is>
           <t>2026-03-24 20:26</t>
         </is>
       </c>
-      <c r="R67" s="6" t="inlineStr">
+      <c r="R67" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="S67" s="3" t="n">
-        <v>343.7</v>
+        <v>301.1</v>
       </c>
       <c r="T67" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U67" s="3" t="n">
-        <v>68.7</v>
+        <v>60.2</v>
       </c>
       <c r="V67" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W67" s="3" t="inlineStr">
@@ -7320,23 +7328,23 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>STD-067</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>فرح زكريا</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -7349,7 +7357,7 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
@@ -7362,7 +7370,7 @@
         </is>
       </c>
       <c r="J68" s="3" t="n">
-        <v>78.7</v>
+        <v>61.4</v>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
@@ -7375,7 +7383,7 @@
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -7388,7 +7396,7 @@
         </is>
       </c>
       <c r="P68" s="3" t="n">
-        <v>83.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
@@ -7401,17 +7409,17 @@
         </is>
       </c>
       <c r="S68" s="3" t="n">
-        <v>410.6</v>
+        <v>324.4</v>
       </c>
       <c r="T68" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="V68" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W68" s="3" t="inlineStr">
@@ -7421,98 +7429,98 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>STD-068</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>سندس خيري</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="D69" s="7" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>2026-01-25 11:09</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G69" s="6" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="G69" s="7" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>2026-02-09 11:52</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="J69" s="6" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="K69" s="6" t="inlineStr">
+      <c r="J69" s="7" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
         <is>
           <t>2026-02-24 08:22</t>
         </is>
       </c>
-      <c r="L69" s="6" t="inlineStr">
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="M69" s="6" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="N69" s="6" t="inlineStr">
+      <c r="M69" s="7" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
         <is>
           <t>2026-03-08 09:09</t>
         </is>
       </c>
-      <c r="O69" s="6" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="P69" s="6" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="Q69" s="6" t="inlineStr">
+      <c r="P69" s="7" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
         <is>
           <t>2026-03-25 21:00</t>
         </is>
       </c>
-      <c r="R69" s="6" t="inlineStr">
+      <c r="R69" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="S69" s="3" t="n">
-        <v>332.1</v>
+        <v>304.4</v>
       </c>
       <c r="T69" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="V69" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W69" s="3" t="inlineStr">
@@ -7522,98 +7530,98 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>STD-069</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>ابتسام عوض</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D70" s="6" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="D70" s="7" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>2026-01-26 12:54</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G70" s="6" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="G70" s="7" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>2026-02-11 17:04</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="J70" s="6" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="K70" s="6" t="inlineStr">
+      <c r="J70" s="7" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>2026-02-26 14:58</t>
         </is>
       </c>
-      <c r="L70" s="6" t="inlineStr">
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="M70" s="6" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="N70" s="6" t="inlineStr">
+      <c r="M70" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
         <is>
           <t>2026-03-11 14:31</t>
         </is>
       </c>
-      <c r="O70" s="6" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="P70" s="6" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="Q70" s="6" t="inlineStr">
+      <c r="P70" s="7" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
         <is>
           <t>2026-03-22 15:39</t>
         </is>
       </c>
-      <c r="R70" s="6" t="inlineStr">
+      <c r="R70" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="S70" s="3" t="n">
-        <v>338</v>
+        <v>318.2</v>
       </c>
       <c r="T70" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="V70" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="W70" s="3" t="inlineStr">
@@ -7623,23 +7631,23 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>STD-070</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>آلاء ثروت</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>89.7</v>
+        <v>89.2</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -7652,7 +7660,7 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
@@ -7665,7 +7673,7 @@
         </is>
       </c>
       <c r="J71" s="3" t="n">
-        <v>90.2</v>
+        <v>89.5</v>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
@@ -7678,7 +7686,7 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
@@ -7691,7 +7699,7 @@
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
@@ -7704,13 +7712,13 @@
         </is>
       </c>
       <c r="S71" s="3" t="n">
-        <v>456.7</v>
+        <v>453.2</v>
       </c>
       <c r="T71" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>91.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V71" s="4" t="inlineStr">
         <is>
@@ -7724,23 +7732,23 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>STD-071</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>كوثر جلال</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>76.7</v>
+        <v>79.8</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -7753,7 +7761,7 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>82.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
@@ -7766,7 +7774,7 @@
         </is>
       </c>
       <c r="J72" s="3" t="n">
-        <v>81.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
@@ -7779,7 +7787,7 @@
         </is>
       </c>
       <c r="M72" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
@@ -7792,7 +7800,7 @@
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>90.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
@@ -7805,17 +7813,17 @@
         </is>
       </c>
       <c r="S72" s="3" t="n">
-        <v>415.3</v>
+        <v>426.1</v>
       </c>
       <c r="T72" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="V72" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>85.2</v>
+      </c>
+      <c r="V72" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="W72" s="3" t="inlineStr">
@@ -7825,23 +7833,23 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>STD-072</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>خلود يحيى</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>66.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -7854,7 +7862,7 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
@@ -7867,7 +7875,7 @@
         </is>
       </c>
       <c r="J73" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
@@ -7880,7 +7888,7 @@
         </is>
       </c>
       <c r="M73" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
@@ -7893,7 +7901,7 @@
         </is>
       </c>
       <c r="P73" s="3" t="n">
-        <v>80.3</v>
+        <v>92.3</v>
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
@@ -7906,17 +7914,17 @@
         </is>
       </c>
       <c r="S73" s="3" t="n">
-        <v>362.3</v>
+        <v>422.7</v>
       </c>
       <c r="T73" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>72.5</v>
+        <v>84.5</v>
       </c>
       <c r="V73" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W73" s="3" t="inlineStr">
@@ -7926,23 +7934,23 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>STD-073</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>بثينة حمزة</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>79.8</v>
+        <v>81</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -7955,7 +7963,7 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>78</v>
+        <v>79.5</v>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
@@ -7968,7 +7976,7 @@
         </is>
       </c>
       <c r="J74" s="3" t="n">
-        <v>81</v>
+        <v>82.8</v>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
@@ -7981,7 +7989,7 @@
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>85.5</v>
+        <v>87.7</v>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
@@ -7994,7 +8002,7 @@
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
@@ -8007,13 +8015,13 @@
         </is>
       </c>
       <c r="S74" s="3" t="n">
-        <v>412.4</v>
+        <v>421.6</v>
       </c>
       <c r="T74" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>82.5</v>
+        <v>84.3</v>
       </c>
       <c r="V74" s="3" t="inlineStr">
         <is>
@@ -8027,23 +8035,23 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>STD-074</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>سمية رجب</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>81.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -8056,7 +8064,7 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
@@ -8069,7 +8077,7 @@
         </is>
       </c>
       <c r="J75" s="3" t="n">
-        <v>87.3</v>
+        <v>84.7</v>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
@@ -8082,7 +8090,7 @@
         </is>
       </c>
       <c r="M75" s="3" t="n">
-        <v>86.8</v>
+        <v>84.3</v>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
@@ -8095,7 +8103,7 @@
         </is>
       </c>
       <c r="P75" s="3" t="n">
-        <v>90.7</v>
+        <v>88.2</v>
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
@@ -8108,17 +8116,17 @@
         </is>
       </c>
       <c r="S75" s="3" t="n">
-        <v>434.9</v>
+        <v>422.1</v>
       </c>
       <c r="T75" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="V75" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="W75" s="3" t="inlineStr">
@@ -8128,23 +8136,23 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>STD-075</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>وجدان صبحي</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>56.1</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -8157,7 +8165,7 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>60.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
@@ -8170,7 +8178,7 @@
         </is>
       </c>
       <c r="J76" s="3" t="n">
-        <v>64.3</v>
+        <v>87.7</v>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
@@ -8183,7 +8191,7 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>70.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
@@ -8196,7 +8204,7 @@
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
@@ -8209,17 +8217,17 @@
         </is>
       </c>
       <c r="S76" s="3" t="n">
-        <v>327.5</v>
+        <v>442.9</v>
       </c>
       <c r="T76" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="V76" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="V76" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="W76" s="3" t="inlineStr">
@@ -8229,98 +8237,98 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>STD-076</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>نرمين شاكر</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D77" s="6" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="D77" s="7" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>2026-01-27 17:10</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G77" s="6" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="G77" s="7" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>2026-02-08 12:21</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="J77" s="6" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="K77" s="6" t="inlineStr">
+      <c r="J77" s="7" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>2026-02-23 22:42</t>
         </is>
       </c>
-      <c r="L77" s="6" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="M77" s="6" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N77" s="6" t="inlineStr">
+      <c r="M77" s="7" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
         <is>
           <t>2026-03-12 13:44</t>
         </is>
       </c>
-      <c r="O77" s="6" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="P77" s="6" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="Q77" s="6" t="inlineStr">
+      <c r="P77" s="7" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="Q77" s="7" t="inlineStr">
         <is>
           <t>2026-03-23 19:23</t>
         </is>
       </c>
-      <c r="R77" s="6" t="inlineStr">
+      <c r="R77" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="S77" s="3" t="n">
-        <v>303.3</v>
+        <v>359.9</v>
       </c>
       <c r="T77" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>60.7</v>
+        <v>72</v>
       </c>
       <c r="V77" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W77" s="3" t="inlineStr">
@@ -8330,98 +8338,98 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>STD-077</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>تغريد لطفي</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D78" s="6" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="D78" s="7" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>2026-01-25 14:53</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="G78" s="6" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="G78" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
         <is>
           <t>2026-02-10 16:08</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="J78" s="6" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="K78" s="6" t="inlineStr">
+      <c r="J78" s="7" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
         <is>
           <t>2026-02-24 18:35</t>
         </is>
       </c>
-      <c r="L78" s="6" t="inlineStr">
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="M78" s="6" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="N78" s="6" t="inlineStr">
+      <c r="M78" s="7" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="N78" s="7" t="inlineStr">
         <is>
           <t>2026-03-12 15:43</t>
         </is>
       </c>
-      <c r="O78" s="6" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="P78" s="6" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="Q78" s="6" t="inlineStr">
+      <c r="P78" s="7" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="Q78" s="7" t="inlineStr">
         <is>
           <t>2026-03-24 21:19</t>
         </is>
       </c>
-      <c r="R78" s="6" t="inlineStr">
+      <c r="R78" s="7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="S78" s="3" t="n">
-        <v>337.9</v>
+        <v>291.3</v>
       </c>
       <c r="T78" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="V78" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="W78" s="3" t="inlineStr">
@@ -8431,23 +8439,23 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>STD-078</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>ولاء حسان</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>65.2</v>
+        <v>84</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -8460,7 +8468,7 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>61.8</v>
+        <v>80.7</v>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
@@ -8473,7 +8481,7 @@
         </is>
       </c>
       <c r="J79" s="3" t="n">
-        <v>59.8</v>
+        <v>78.8</v>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
@@ -8486,7 +8494,7 @@
         </is>
       </c>
       <c r="M79" s="3" t="n">
-        <v>70.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
@@ -8499,7 +8507,7 @@
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
@@ -8512,17 +8520,17 @@
         </is>
       </c>
       <c r="S79" s="3" t="n">
-        <v>325.4</v>
+        <v>420.3</v>
       </c>
       <c r="T79" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="V79" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W79" s="3" t="inlineStr">
@@ -8532,23 +8540,23 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>STD-079</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>أمنية رأفت</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -8561,7 +8569,7 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
@@ -8574,7 +8582,7 @@
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>69.3</v>
+        <v>76.5</v>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
@@ -8587,7 +8595,7 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>72.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
@@ -8600,7 +8608,7 @@
         </is>
       </c>
       <c r="P80" s="3" t="n">
-        <v>79.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
@@ -8613,17 +8621,17 @@
         </is>
       </c>
       <c r="S80" s="3" t="n">
-        <v>361.6</v>
+        <v>397.3</v>
       </c>
       <c r="T80" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>72.3</v>
+        <v>79.5</v>
       </c>
       <c r="V80" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W80" s="3" t="inlineStr">
@@ -8633,23 +8641,23 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>STD-080</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>يمنى ممدوح</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>73.7</v>
+        <v>77.8</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -8662,7 +8670,7 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>70.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
@@ -8675,7 +8683,7 @@
         </is>
       </c>
       <c r="J81" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
@@ -8688,7 +8696,7 @@
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>79.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
@@ -8701,7 +8709,7 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>76.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
@@ -8714,17 +8722,17 @@
         </is>
       </c>
       <c r="S81" s="3" t="n">
-        <v>373.5</v>
+        <v>390.2</v>
       </c>
       <c r="T81" s="3" t="n">
         <v>500</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>74.7</v>
+        <v>78</v>
       </c>
       <c r="V81" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W81" s="3" t="inlineStr">
@@ -8762,232 +8770,232 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>N_Active</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>M1_Mean</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>M2_Mean</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>M3_Mean</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>M4_Mean</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>M5_Mean</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Total_Mean</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Pct_Mean</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Late_Count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>تنافسي+مفتوح</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="E2" s="10" t="n">
-        <v>71.13</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>73.83</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>74.88</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>81.22</v>
-      </c>
-      <c r="I2" s="10" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="J2" s="10" t="n">
-        <v>379.56</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>75.92</v>
-      </c>
-      <c r="L2" s="10" t="n">
+      <c r="E2" s="11" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>77.52</v>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="L2" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>تنافسي+محدد</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E3" s="11" t="n">
-        <v>70.12</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>72.08</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>71.69</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>72.15000000000001</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>72.56999999999999</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>358.61</v>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>71.72</v>
-      </c>
-      <c r="L3" s="11" t="n">
+      <c r="E3" s="12" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>75.47</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>371.33</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>74.27</v>
+      </c>
+      <c r="L3" s="12" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>تشاركي+مفتوح</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="12" t="n">
-        <v>73.06</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>75.79000000000001</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>79.31</v>
-      </c>
-      <c r="I4" s="12" t="n">
-        <v>84.15000000000001</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>389.9</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>77.98</v>
-      </c>
-      <c r="L4" s="12" t="n">
+      <c r="E4" s="13" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>83.66</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>389.48</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L4" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>تشاركي+محدد</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="E5" s="13" t="n">
-        <v>70.87</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>73.38</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>73.27</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>79.56</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>372.15</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>74.43000000000001</v>
-      </c>
-      <c r="L5" s="13" t="n">
+      <c r="E5" s="14" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>76.13</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>376.94</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="L5" s="14" t="n">
         <v>25</v>
       </c>
     </row>

--- a/tasks_gradebook.xlsx
+++ b/tasks_gradebook.xlsx
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-01-24 19:45</t>
+          <t>2026-01-23 19:47</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -734,11 +734,11 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>66.2</v>
+        <v>51</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 16:07</t>
+          <t>2026-02-04 20:27</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 16:22</t>
+          <t>2026-02-17 11:55</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>84.3</v>
+        <v>71.3</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 19:38</t>
+          <t>2026-03-04 14:49</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>61.7</v>
+        <v>47.5</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 16:26</t>
+          <t>2026-03-20 10:33</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
@@ -789,17 +789,17 @@
         <v>0</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>369.2</v>
+        <v>294.2</v>
       </c>
       <c r="V2" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>73.8</v>
+        <v>58.8</v>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>72.2</v>
+        <v>54.2</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 18:21</t>
+          <t>2026-01-19 15:53</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>82.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 15:53</t>
+          <t>2026-02-03 19:11</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -856,11 +856,11 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 19:11</t>
+          <t>2026-02-16 15:02</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 15:02</t>
+          <t>2026-03-02 19:40</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -882,11 +882,11 @@
         </is>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>80.3</v>
+        <v>62.2</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 21:44</t>
+          <t>2026-03-19 14:58</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
@@ -895,20 +895,20 @@
         </is>
       </c>
       <c r="T3" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>400.4</v>
+        <v>316.6</v>
       </c>
       <c r="V3" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 18:28</t>
+          <t>2026-01-23 16:40</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>69.2</v>
+        <v>58.2</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 22:26</t>
+          <t>2026-02-03 11:49</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -965,11 +965,11 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>68.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 19:49</t>
+          <t>2026-02-19 10:18</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -978,11 +978,11 @@
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 20:23</t>
+          <t>2026-03-04 15:48</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -991,11 +991,11 @@
         </is>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 17:08</t>
+          <t>2026-03-19 21:17</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1004,20 +1004,20 @@
         </is>
       </c>
       <c r="T4" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>378.4</v>
+        <v>332.2</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>75.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>67.8</v>
+        <v>66.8</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 16:27</t>
+          <t>2026-01-21 15:42</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 09:08</t>
+          <t>2026-02-04 16:27</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1074,11 +1074,11 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:40</t>
+          <t>2026-02-18 09:08</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -1087,11 +1087,11 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>77</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 20:33</t>
+          <t>2026-03-02 15:40</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -1100,11 +1100,11 @@
         </is>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>61.4</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:38</t>
+          <t>2026-03-19 20:33</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1116,17 +1116,17 @@
         <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>345.4</v>
+        <v>353</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>77.5</v>
+        <v>61.5</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 12:24</t>
+          <t>2026-01-22 13:26</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1170,11 +1170,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>82.8</v>
+        <v>68.7</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 09:14</t>
+          <t>2026-02-04 12:24</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1183,11 +1183,11 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 20:16</t>
+          <t>2026-02-19 09:14</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1196,11 +1196,11 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 15:39</t>
+          <t>2026-03-05 20:16</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>79.8</v>
+        <v>81</v>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 16:47</t>
+          <t>2026-03-20 10:33</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1222,20 +1222,20 @@
         </is>
       </c>
       <c r="T6" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>421.3</v>
+        <v>366.2</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>84.3</v>
+        <v>73.2</v>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>69.7</v>
+        <v>68.2</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 19:43</t>
+          <t>2026-01-20 10:05</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1279,11 +1279,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>66</v>
+        <v>75.8</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 19:09</t>
+          <t>2026-02-04 18:27</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 22:09</t>
+          <t>2026-02-17 21:30</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>67.8</v>
+        <v>80.3</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 15:26</t>
+          <t>2026-03-02 15:41</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1318,11 +1318,11 @@
         </is>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 12:18</t>
+          <t>2026-03-19 11:22</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1334,17 +1334,17 @@
         <v>0</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>349.5</v>
+        <v>367.7</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1375,11 +1375,11 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 15:41</t>
+          <t>2026-01-22 14:54</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1388,11 +1388,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>68.7</v>
+        <v>70.3</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 19:58</t>
+          <t>2026-02-04 15:15</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>72.7</v>
+        <v>56.8</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:43</t>
+          <t>2026-02-16 12:46</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1414,11 +1414,11 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 19:16</t>
+          <t>2026-03-02 20:26</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 15:54</t>
+          <t>2026-03-19 10:05</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1440,20 +1440,20 @@
         </is>
       </c>
       <c r="T8" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>378.8</v>
+        <v>319.5</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>75.8</v>
+        <v>63.9</v>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1484,11 +1484,11 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>71.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 15:43</t>
+          <t>2026-01-22 15:51</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>55.7</v>
+        <v>74.7</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 13:37</t>
+          <t>2026-02-04 15:43</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>76.5</v>
+        <v>53.1</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 10:38</t>
+          <t>2026-02-18 13:37</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1523,11 +1523,11 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>77.2</v>
+        <v>74.2</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 19:24</t>
+          <t>2026-03-02 10:38</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1536,11 +1536,11 @@
         </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>71.7</v>
+        <v>73.3</v>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:29</t>
+          <t>2026-03-20 20:02</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -1552,17 +1552,17 @@
         <v>0</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>352.8</v>
+        <v>340.7</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -1593,11 +1593,11 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 22:34</t>
+          <t>2026-01-22 13:55</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1606,11 +1606,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 17:35</t>
+          <t>2026-02-04 15:20</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1619,11 +1619,11 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 11:57</t>
+          <t>2026-02-17 13:01</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1632,11 +1632,11 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 15:46</t>
+          <t>2026-03-05 14:28</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>69.2</v>
+        <v>63.2</v>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 12:29</t>
+          <t>2026-03-19 09:04</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1661,17 +1661,17 @@
         <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>364</v>
+        <v>376.4</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>72.8</v>
+        <v>75.3</v>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -1702,11 +1702,11 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>97.8</v>
+        <v>81.7</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 16:31</t>
+          <t>2026-01-20 22:19</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1715,11 +1715,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>81.2</v>
+        <v>94.8</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 12:01</t>
+          <t>2026-02-04 20:26</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1728,11 +1728,11 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 09:53</t>
+          <t>2026-02-17 14:49</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1741,11 +1741,11 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 13:33</t>
+          <t>2026-03-02 16:08</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1754,11 +1754,11 @@
         </is>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>85.2</v>
+        <v>61.7</v>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 18:40</t>
+          <t>2026-03-19 13:06</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -1770,17 +1770,17 @@
         <v>5</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>406.9</v>
+        <v>396.7</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1811,11 +1811,11 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>89.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 12:02</t>
+          <t>2026-01-21 22:13</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1824,11 +1824,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>100</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 16:22</t>
+          <t>2026-02-04 10:33</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1837,11 +1837,11 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 15:48</t>
+          <t>2026-02-16 13:49</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1850,11 +1850,11 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>100</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 11:57</t>
+          <t>2026-03-02 22:19</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -1863,11 +1863,11 @@
         </is>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>88.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:30</t>
+          <t>2026-03-19 17:17</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -1876,20 +1876,20 @@
         </is>
       </c>
       <c r="T12" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>485.9</v>
+        <v>410.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -1920,11 +1920,11 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>63.4</v>
+        <v>70.8</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 11:53</t>
+          <t>2026-01-23 11:53</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>62.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>74.2</v>
+        <v>70.8</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>69</v>
+        <v>82.3</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>63.8</v>
+        <v>75.5</v>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
@@ -1988,17 +1988,17 @@
         <v>0</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>332.9</v>
+        <v>374</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>74.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2042,11 +2042,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>85.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 19:10</t>
+          <t>2026-02-03 19:10</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>65.8</v>
+        <v>68</v>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
@@ -2097,17 +2097,17 @@
         <v>0</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>369.3</v>
+        <v>382.5</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>79.5</v>
+        <v>75.5</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>86.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>87</v>
+        <v>80.7</v>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
@@ -2203,20 +2203,20 @@
         </is>
       </c>
       <c r="T15" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>441.4</v>
+        <v>407.8</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>56.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>61.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>75.5</v>
+        <v>92.2</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>73.8</v>
+        <v>88.7</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>81.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
@@ -2312,20 +2312,20 @@
         </is>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>74.7</v>
+        <v>78</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>76.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>84.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
@@ -2421,20 +2421,20 @@
         </is>
       </c>
       <c r="T17" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>369.8</v>
+        <v>391.6</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>74</v>
+        <v>78.3</v>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>66</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
@@ -2530,16 +2530,16 @@
         </is>
       </c>
       <c r="T18" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>397.9</v>
+        <v>384.7</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>68.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>66.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
@@ -2639,20 +2639,20 @@
         </is>
       </c>
       <c r="T19" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>365.1</v>
+        <v>395</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>57.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>76.2</v>
+        <v>99.5</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>68.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>59.8</v>
+        <v>79.8</v>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
@@ -2748,20 +2748,20 @@
         </is>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>339.4</v>
+        <v>456.5</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="X20" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>91.3</v>
+      </c>
+      <c r="X20" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>70.8</v>
+        <v>88.5</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
@@ -2857,20 +2857,20 @@
         </is>
       </c>
       <c r="T21" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>351</v>
+        <v>452.6</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>90.5</v>
+      </c>
+      <c r="X21" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>58.3</v>
+        <v>50.4</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="K22" s="6" t="n">
-        <v>51.9</v>
+        <v>45.9</v>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
@@ -2940,11 +2940,11 @@
         </is>
       </c>
       <c r="N22" s="6" t="n">
-        <v>52.3</v>
+        <v>45.3</v>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 22:48</t>
+          <t>2026-03-06 22:12</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>78.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
@@ -2969,17 +2969,17 @@
         <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>311.4</v>
+        <v>270.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t>D+</t>
+        <v>54.2</v>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3010,11 +3010,11 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>51.2</v>
+        <v>44.9</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:24</t>
+          <t>2026-01-23 18:18</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>30.2</v>
+        <v>27.1</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="K23" s="6" t="n">
-        <v>41.2</v>
+        <v>34.5</v>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
@@ -3049,11 +3049,11 @@
         </is>
       </c>
       <c r="N23" s="6" t="n">
-        <v>27.4</v>
+        <v>43.4</v>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 20:18</t>
+          <t>2026-03-06 21:36</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>67.8</v>
+        <v>60.6</v>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
@@ -3078,13 +3078,13 @@
         <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>217.8</v>
+        <v>210.5</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>43.6</v>
+        <v>42.1</v>
       </c>
       <c r="X23" s="7" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>72.5</v>
+        <v>59.9</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>85.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>83.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>68.2</v>
+        <v>54.9</v>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
@@ -3171,11 +3171,11 @@
         </is>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>51</v>
+        <v>40.7</v>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 20:06</t>
+          <t>2026-03-20 22:24</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
@@ -3184,20 +3184,20 @@
         </is>
       </c>
       <c r="T24" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>376.3</v>
+        <v>307.3</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>75.3</v>
+        <v>61.5</v>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3227,25 +3227,25 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 01:46</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E25" s="6" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 21:30</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>63.1</v>
+        <v>61</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 10:09</t>
+          <t>2026-02-05 23:20</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3254,11 +3254,11 @@
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>52.9</v>
+        <v>51.9</v>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>2026-02-20 18:42</t>
+          <t>2026-02-20 21:00</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -3267,11 +3267,11 @@
         </is>
       </c>
       <c r="N25" s="6" t="n">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 19:24</t>
+          <t>2026-03-06 20:54</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
@@ -3280,11 +3280,11 @@
         </is>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>68.5</v>
+        <v>66.3</v>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:13</t>
+          <t>2026-03-19 06:30</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3296,17 +3296,17 @@
         <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>304.2</v>
+        <v>274</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t>D+</t>
+        <v>54.8</v>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3336,25 +3336,25 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 23:09</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E26" s="6" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 18:18</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>59.7</v>
+        <v>82.7</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 11:31</t>
+          <t>2026-02-05 18:37</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3362,25 +3362,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 17:05</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K26" s="6" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-21 11:30</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>50.3</v>
+        <v>56.8</v>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 15:10</t>
+          <t>2026-03-06 05:51</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3389,11 +3389,11 @@
         </is>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>57.1</v>
+        <v>63.1</v>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 19:18</t>
+          <t>2026-03-20 13:41</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3402,20 +3402,20 @@
         </is>
       </c>
       <c r="T26" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>307.6</v>
+        <v>284.6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>61.5</v>
+        <v>56.9</v>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>80.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -3459,21 +3459,21 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06 06:15</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n">
         <v>74.2</v>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 06:15</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
           <t>2026-02-19 20:31</t>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>81</v>
+        <v>71.8</v>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
@@ -3498,11 +3498,11 @@
         </is>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>32</v>
+        <v>28.1</v>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 18:06</t>
+          <t>2026-03-20 21:06</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
@@ -3514,17 +3514,17 @@
         <v>10</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>361.1</v>
+        <v>327</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>72.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>49.9</v>
+        <v>55.2</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>83.8</v>
+        <v>87.5</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>73.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
@@ -3623,17 +3623,17 @@
         <v>20</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>364.7</v>
+        <v>377.6</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>28.5</v>
+        <v>27.8</v>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 19:12</t>
+          <t>2026-02-06 18:24</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>64</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>78</v>
+        <v>73.3</v>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
@@ -3716,11 +3716,11 @@
         </is>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>54.8</v>
+        <v>51.4</v>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 18:36</t>
+          <t>2026-03-20 18:54</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>269.6</v>
+        <v>255.5</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>53.9</v>
+        <v>51.1</v>
       </c>
       <c r="X29" s="7" t="inlineStr">
         <is>
@@ -3773,11 +3773,11 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>45.7</v>
+        <v>47.4</v>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:54</t>
+          <t>2026-01-23 19:00</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>68.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>88</v>
+        <v>94.8</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>81</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>72.7</v>
+        <v>76.3</v>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
@@ -3838,20 +3838,20 @@
         </is>
       </c>
       <c r="T30" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>366.2</v>
+        <v>389.3</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>73.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -3882,11 +3882,11 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>51.4</v>
+        <v>27.6</v>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 19:42</t>
+          <t>2026-01-23 22:18</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>77</v>
+        <v>79.3</v>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
@@ -3934,11 +3934,11 @@
         </is>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>56.1</v>
+        <v>58.3</v>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 20:06</t>
+          <t>2026-03-20 18:48</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
@@ -3950,17 +3950,17 @@
         <v>0</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>66.2</v>
+        <v>62.2</v>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>76.5</v>
+        <v>72.5</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>86</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>81.3</v>
+        <v>78</v>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
@@ -4059,17 +4059,17 @@
         <v>20</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>433.5</v>
+        <v>416.8</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="X32" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>83.40000000000001</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>63.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -4113,11 +4113,11 @@
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 22:54</t>
+          <t>2026-02-06 21:06</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
@@ -4126,11 +4126,11 @@
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>47.9</v>
+        <v>46.8</v>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>2026-02-20 20:06</t>
+          <t>2026-02-20 19:00</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -4139,11 +4139,11 @@
         </is>
       </c>
       <c r="N33" s="6" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 22:30</t>
+          <t>2026-03-06 21:30</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
@@ -4152,11 +4152,11 @@
         </is>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>53.9</v>
+        <v>52.8</v>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 22:48</t>
+          <t>2026-03-20 19:24</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
@@ -4168,13 +4168,13 @@
         <v>0</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>221</v>
+        <v>223.1</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>44.2</v>
+        <v>44.6</v>
       </c>
       <c r="X33" s="7" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>70.2</v>
+        <v>83.8</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>70.3</v>
+        <v>85.7</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>58</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>64.8</v>
+        <v>80.7</v>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
@@ -4261,11 +4261,11 @@
         </is>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>22.3</v>
+        <v>28.3</v>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 20:48</t>
+          <t>2026-03-20 22:48</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
@@ -4274,20 +4274,20 @@
         </is>
       </c>
       <c r="T34" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>285.6</v>
+        <v>366.9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>57.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>55.1</v>
+        <v>69.3</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -4330,25 +4330,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 06:14</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H35" s="6" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 21:48</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>45.8</v>
+        <v>52.8</v>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>2026-02-20 20:24</t>
+          <t>2026-02-20 20:06</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
@@ -4357,11 +4357,11 @@
         </is>
       </c>
       <c r="N35" s="6" t="n">
-        <v>51.7</v>
+        <v>58.6</v>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 22:00</t>
+          <t>2026-03-06 18:54</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
@@ -4370,11 +4370,11 @@
         </is>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>51.3</v>
+        <v>58.4</v>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 18:42</t>
+          <t>2026-03-20 21:30</t>
         </is>
       </c>
       <c r="S35" s="6" t="inlineStr">
@@ -4386,17 +4386,17 @@
         <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>270.3</v>
+        <v>293.2</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="X35" s="7" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>58.6</v>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>61.3</v>
+        <v>73.3</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>64</v>
+        <v>70.2</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
@@ -4465,25 +4465,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 19:05</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N36" s="6" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 17:06</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>81.3</v>
+        <v>89.3</v>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 10:46</t>
+          <t>2026-03-19 18:19</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -4492,20 +4492,20 @@
         </is>
       </c>
       <c r="T36" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>382.9</v>
+        <v>369</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -4536,11 +4536,11 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>61.4</v>
+        <v>47.8</v>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 19:00</t>
+          <t>2026-01-23 20:30</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -4548,25 +4548,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 19:05</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H37" s="6" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 22:06</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>76.7</v>
+        <v>68.5</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 04:12</t>
+          <t>2026-02-20 10:38</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -4574,25 +4574,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N37" s="3" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 15:28</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N37" s="6" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:36</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>57.2</v>
+        <v>51.6</v>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 18:18</t>
+          <t>2026-03-20 22:24</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
@@ -4604,17 +4604,17 @@
         <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>371.9</v>
+        <v>282.1</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -4644,38 +4644,38 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 18:12</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 06:48</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E38" s="6" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:18</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-07 15:18</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>70.7</v>
+        <v>73.2</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 15:46</t>
+          <t>2026-02-19 12:42</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4684,11 +4684,11 @@
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>62.6</v>
+        <v>64.5</v>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 06:47</t>
+          <t>2026-03-05 08:55</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -4697,11 +4697,11 @@
         </is>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>74.3</v>
+        <v>90.3</v>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:18</t>
+          <t>2026-03-19 11:17</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -4710,20 +4710,20 @@
         </is>
       </c>
       <c r="T38" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>346.5</v>
+        <v>322.8</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>69.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -4753,64 +4753,64 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 23:00</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 19:54</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="E39" s="6" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:36</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K39" s="6" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 18:06</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="H39" s="3" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06 16:12</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-20 03:53</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:24</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="N39" s="6" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="O39" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:36</t>
-        </is>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
       <c r="Q39" s="6" t="n">
-        <v>23.4</v>
+        <v>54.8</v>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 19:48</t>
+          <t>2026-03-20 19:06</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
@@ -4822,17 +4822,17 @@
         <v>0</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>190.4</v>
+        <v>293.1</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="X39" s="7" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>58.6</v>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -4863,11 +4863,11 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>31.3</v>
+        <v>52.2</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:36</t>
+          <t>2026-01-23 21:36</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -4876,11 +4876,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>50.7</v>
+        <v>73.2</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 05:34</t>
+          <t>2026-02-06 19:06</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4889,11 +4889,11 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 18:17</t>
+          <t>2026-02-19 17:26</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -4902,11 +4902,11 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 15:16</t>
+          <t>2026-03-05 01:26</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4914,34 +4914,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 19:04</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="Q40" s="6" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-20 21:24</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T40" s="3" t="n">
         <v>10</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>313</v>
+        <v>369.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>62.6</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -4971,51 +4971,51 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 18:54</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="E41" s="3" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 06:59</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 20:50</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 22:24</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 18:25</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 09:31</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="N41" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 07:52</t>
+          <t>2026-03-06 08:37</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5024,11 +5024,11 @@
         </is>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>73.2</v>
+        <v>89</v>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:30</t>
+          <t>2026-03-19 15:30</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -5037,20 +5037,20 @@
         </is>
       </c>
       <c r="T41" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>366.5</v>
+        <v>435.3</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>87.09999999999999</v>
+      </c>
+      <c r="X41" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5081,11 +5081,11 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 13:19</t>
+          <t>2026-01-20 13:31</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5094,11 +5094,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 13:52</t>
+          <t>2026-02-05 12:35</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5107,11 +5107,11 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>93.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 09:33</t>
+          <t>2026-02-17 09:17</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5120,11 +5120,11 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>84.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 17:47</t>
+          <t>2026-03-04 13:19</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5133,11 +5133,11 @@
         </is>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 21:28</t>
+          <t>2026-03-19 13:52</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -5149,17 +5149,17 @@
         <v>0</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>403.9</v>
+        <v>361.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>80.8</v>
+        <v>72.3</v>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5190,11 +5190,11 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 14:39</t>
+          <t>2026-01-21 22:59</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5203,11 +5203,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 19:30</t>
+          <t>2026-02-04 12:48</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5216,11 +5216,11 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 10:02</t>
+          <t>2026-02-18 12:47</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5229,11 +5229,11 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 19:06</t>
+          <t>2026-03-04 11:33</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5242,11 +5242,11 @@
         </is>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>88.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:14</t>
+          <t>2026-03-19 14:39</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -5255,16 +5255,16 @@
         </is>
       </c>
       <c r="T43" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>431.7</v>
+        <v>442.3</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>86.3</v>
+        <v>88.5</v>
       </c>
       <c r="X43" s="4" t="inlineStr">
         <is>
@@ -5295,15 +5295,15 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>70.7</v>
+        <v>69.2</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 17:23</t>
+          <t>2026-01-21 13:02</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -5312,11 +5312,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 21:41</t>
+          <t>2026-02-05 17:03</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5325,11 +5325,11 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>89.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 22:18</t>
+          <t>2026-02-18 12:30</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -5338,11 +5338,11 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:24</t>
+          <t>2026-03-02 09:03</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5351,11 +5351,11 @@
         </is>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:06</t>
+          <t>2026-03-19 17:23</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -5367,17 +5367,17 @@
         <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>407.5</v>
+        <v>387.1</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>81.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -5408,11 +5408,11 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 13:26</t>
+          <t>2026-01-20 13:43</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -5421,11 +5421,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 14:05</t>
+          <t>2026-02-05 12:36</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -5434,11 +5434,11 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>93.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 09:36</t>
+          <t>2026-02-17 09:31</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -5447,11 +5447,11 @@
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>84.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 17:48</t>
+          <t>2026-03-04 13:30</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 21:30</t>
+          <t>2026-03-19 13:59</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -5476,17 +5476,17 @@
         <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>403.9</v>
+        <v>361.6</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>80.8</v>
+        <v>72.3</v>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -5517,11 +5517,11 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>68.7</v>
+        <v>77</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 16:13</t>
+          <t>2026-01-22 11:09</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -5530,11 +5530,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>70.2</v>
+        <v>78.2</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 13:54</t>
+          <t>2026-02-04 09:16</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5543,11 +5543,11 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>89.5</v>
+        <v>93.3</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 15:20</t>
+          <t>2026-02-19 15:24</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5556,11 +5556,11 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>78.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:14</t>
+          <t>2026-03-04 15:28</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -5569,11 +5569,11 @@
         </is>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>76.8</v>
+        <v>87.5</v>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 22:29</t>
+          <t>2026-03-19 20:13</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -5585,17 +5585,17 @@
         <v>0</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>383.9</v>
+        <v>419.4</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>76.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -5622,15 +5622,15 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>77.8</v>
+        <v>70.7</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 15:55</t>
+          <t>2026-01-20 13:28</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -5639,11 +5639,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 11:09</t>
+          <t>2026-02-04 09:51</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5652,11 +5652,11 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 10:28</t>
+          <t>2026-02-17 18:36</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -5665,11 +5665,11 @@
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>83.5</v>
+        <v>94.3</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:13</t>
+          <t>2026-03-03 09:01</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -5678,11 +5678,11 @@
         </is>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>86.3</v>
+        <v>91</v>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:29</t>
+          <t>2026-03-19 21:55</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -5694,13 +5694,13 @@
         <v>25</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>445.6</v>
+        <v>447.6</v>
       </c>
       <c r="V47" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W47" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="X47" s="4" t="inlineStr">
         <is>
@@ -5731,15 +5731,15 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 14:40</t>
+          <t>2026-01-21 13:05</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5748,11 +5748,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 19:35</t>
+          <t>2026-02-05 17:16</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5761,11 +5761,11 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 10:15</t>
+          <t>2026-02-18 12:31</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -5774,11 +5774,11 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 19:14</t>
+          <t>2026-03-02 09:06</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -5787,11 +5787,11 @@
         </is>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>88.5</v>
+        <v>72</v>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:24</t>
+          <t>2026-03-19 17:25</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -5800,20 +5800,20 @@
         </is>
       </c>
       <c r="T48" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>431.7</v>
+        <v>387.1</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W48" s="3" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="X48" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -5844,11 +5844,11 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>68.7</v>
+        <v>77</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 16:20</t>
+          <t>2026-01-22 11:20</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5857,11 +5857,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>70.2</v>
+        <v>78.2</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 13:57</t>
+          <t>2026-02-04 09:26</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5870,11 +5870,11 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>89.5</v>
+        <v>93.3</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 15:34</t>
+          <t>2026-02-19 15:32</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -5883,11 +5883,11 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>78.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:26</t>
+          <t>2026-03-04 15:32</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5896,11 +5896,11 @@
         </is>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>76.8</v>
+        <v>87.5</v>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 22:44</t>
+          <t>2026-03-19 20:15</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -5912,17 +5912,17 @@
         <v>0</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>383.9</v>
+        <v>419.4</v>
       </c>
       <c r="V49" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>76.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
@@ -5949,15 +5949,15 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>68.7</v>
+        <v>63.9</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 16:26</t>
+          <t>2026-01-20 13:40</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5966,11 +5966,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>70.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 13:59</t>
+          <t>2026-02-05 12:39</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5979,11 +5979,11 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>89.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 15:24</t>
+          <t>2026-02-17 09:26</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -5992,11 +5992,11 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>78.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:18</t>
+          <t>2026-03-04 13:30</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -6005,11 +6005,11 @@
         </is>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>76.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 22:43</t>
+          <t>2026-03-19 14:05</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -6021,17 +6021,17 @@
         <v>0</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>383.9</v>
+        <v>361.6</v>
       </c>
       <c r="V50" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W50" s="3" t="n">
-        <v>76.8</v>
+        <v>72.3</v>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -6058,15 +6058,15 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 14:48</t>
+          <t>2026-01-21 13:10</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -6075,11 +6075,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 19:37</t>
+          <t>2026-02-05 17:04</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -6088,11 +6088,11 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 10:17</t>
+          <t>2026-02-18 12:35</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6101,11 +6101,11 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 19:16</t>
+          <t>2026-03-02 09:16</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -6114,11 +6114,11 @@
         </is>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>88.5</v>
+        <v>72</v>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:28</t>
+          <t>2026-03-19 17:31</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -6127,20 +6127,20 @@
         </is>
       </c>
       <c r="T51" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>431.7</v>
+        <v>387.1</v>
       </c>
       <c r="V51" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="X51" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
@@ -6167,15 +6167,15 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 22:30</t>
+          <t>2026-01-22 17:58</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -6184,11 +6184,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 14:49</t>
+          <t>2026-02-02 17:04</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -6197,11 +6197,11 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>93.2</v>
+        <v>88.3</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 10:44</t>
+          <t>2026-02-18 14:08</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>85.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 13:42</t>
+          <t>2026-03-02 13:06</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -6223,11 +6223,11 @@
         </is>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>86</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:50</t>
+          <t>2026-03-19 17:30</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -6236,16 +6236,16 @@
         </is>
       </c>
       <c r="T52" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>438.5</v>
+        <v>435.4</v>
       </c>
       <c r="V52" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W52" s="3" t="n">
-        <v>87.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="X52" s="4" t="inlineStr">
         <is>
@@ -6276,15 +6276,15 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 22:41</t>
+          <t>2026-01-22 18:05</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -6293,11 +6293,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 14:54</t>
+          <t>2026-02-02 17:14</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>93.2</v>
+        <v>88.3</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 10:56</t>
+          <t>2026-02-18 14:13</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6319,11 +6319,11 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>85.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 13:55</t>
+          <t>2026-03-02 13:19</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -6332,11 +6332,11 @@
         </is>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>86</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:55</t>
+          <t>2026-03-19 17:32</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -6345,16 +6345,16 @@
         </is>
       </c>
       <c r="T53" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>438.5</v>
+        <v>435.4</v>
       </c>
       <c r="V53" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W53" s="3" t="n">
-        <v>87.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="X53" s="4" t="inlineStr">
         <is>
@@ -6385,15 +6385,15 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>77.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 15:57</t>
+          <t>2026-01-21 23:12</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -6402,11 +6402,11 @@
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 11:23</t>
+          <t>2026-02-04 12:49</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -6415,11 +6415,11 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 10:31</t>
+          <t>2026-02-18 12:59</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6428,11 +6428,11 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>83.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:22</t>
+          <t>2026-03-04 11:39</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -6441,11 +6441,11 @@
         </is>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>86.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:33</t>
+          <t>2026-03-19 14:45</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -6454,16 +6454,16 @@
         </is>
       </c>
       <c r="T54" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>445.6</v>
+        <v>442.3</v>
       </c>
       <c r="V54" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="X54" s="4" t="inlineStr">
         <is>
@@ -6498,11 +6498,11 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>77.8</v>
+        <v>78.5</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 15:57</t>
+          <t>2026-01-22 17:59</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -6511,11 +6511,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 11:21</t>
+          <t>2026-02-02 17:15</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -6524,11 +6524,11 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 10:31</t>
+          <t>2026-02-18 14:11</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6537,11 +6537,11 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>83.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:24</t>
+          <t>2026-03-02 13:16</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -6550,11 +6550,11 @@
         </is>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>86.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:40</t>
+          <t>2026-03-19 17:41</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -6563,16 +6563,16 @@
         </is>
       </c>
       <c r="T55" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>445.6</v>
+        <v>435.4</v>
       </c>
       <c r="V55" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="X55" s="4" t="inlineStr">
         <is>
@@ -6603,15 +6603,15 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>70.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 17:24</t>
+          <t>2026-01-21 23:12</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -6620,11 +6620,11 @@
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 21:44</t>
+          <t>2026-02-04 12:59</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6633,11 +6633,11 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>89.2</v>
+        <v>92.8</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 22:30</t>
+          <t>2026-02-18 12:52</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6646,11 +6646,11 @@
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:32</t>
+          <t>2026-03-04 11:45</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -6659,11 +6659,11 @@
         </is>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:08</t>
+          <t>2026-03-19 14:52</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -6672,20 +6672,20 @@
         </is>
       </c>
       <c r="T56" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>407.5</v>
+        <v>442.3</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="X56" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>88.5</v>
+      </c>
+      <c r="X56" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 17:38</t>
+          <t>2026-01-20 13:33</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -6729,11 +6729,11 @@
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 21:45</t>
+          <t>2026-02-04 09:53</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6742,11 +6742,11 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>89.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 22:19</t>
+          <t>2026-02-17 18:50</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -6755,11 +6755,11 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:38</t>
+          <t>2026-03-03 09:04</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -6768,11 +6768,11 @@
         </is>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:07</t>
+          <t>2026-03-19 22:04</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -6781,20 +6781,20 @@
         </is>
       </c>
       <c r="T57" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>407.5</v>
+        <v>447.6</v>
       </c>
       <c r="V57" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W57" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="X57" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>89.5</v>
+      </c>
+      <c r="X57" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -6821,15 +6821,15 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>70.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 17:32</t>
+          <t>2026-01-21 23:03</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6838,11 +6838,11 @@
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 21:56</t>
+          <t>2026-02-04 12:50</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6851,11 +6851,11 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>89.2</v>
+        <v>92.8</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 22:27</t>
+          <t>2026-02-18 12:59</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -6864,11 +6864,11 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:33</t>
+          <t>2026-03-04 11:36</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -6877,11 +6877,11 @@
         </is>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:12</t>
+          <t>2026-03-19 14:50</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -6890,20 +6890,20 @@
         </is>
       </c>
       <c r="T58" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>407.5</v>
+        <v>442.3</v>
       </c>
       <c r="V58" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W58" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="X58" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>88.5</v>
+      </c>
+      <c r="X58" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -6934,11 +6934,11 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>77.8</v>
+        <v>78.5</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 15:57</t>
+          <t>2026-01-22 18:09</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -6947,11 +6947,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 11:18</t>
+          <t>2026-02-02 17:05</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 10:42</t>
+          <t>2026-02-18 14:11</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -6973,11 +6973,11 @@
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>83.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:15</t>
+          <t>2026-03-02 13:18</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -6986,11 +6986,11 @@
         </is>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>86.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:43</t>
+          <t>2026-03-19 17:38</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -6999,16 +6999,16 @@
         </is>
       </c>
       <c r="T59" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>445.6</v>
+        <v>435.4</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="X59" s="4" t="inlineStr">
         <is>
@@ -7039,15 +7039,15 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>68.7</v>
+        <v>70.7</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 16:20</t>
+          <t>2026-01-20 13:30</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -7056,11 +7056,11 @@
         </is>
       </c>
       <c r="H60" s="3" t="n">
-        <v>70.2</v>
+        <v>77</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:03</t>
+          <t>2026-02-04 10:06</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -7069,11 +7069,11 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>89.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 15:23</t>
+          <t>2026-02-17 18:40</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7082,11 +7082,11 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>78.7</v>
+        <v>94.3</v>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:24</t>
+          <t>2026-03-03 09:02</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -7095,11 +7095,11 @@
         </is>
       </c>
       <c r="Q60" s="3" t="n">
-        <v>76.8</v>
+        <v>91</v>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 22:32</t>
+          <t>2026-03-19 22:09</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -7108,20 +7108,20 @@
         </is>
       </c>
       <c r="T60" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>383.9</v>
+        <v>447.6</v>
       </c>
       <c r="V60" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W60" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="X60" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>89.5</v>
+      </c>
+      <c r="X60" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -7148,15 +7148,15 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 22:35</t>
+          <t>2026-01-22 11:10</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -7165,11 +7165,11 @@
         </is>
       </c>
       <c r="H61" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 15:00</t>
+          <t>2026-02-04 09:25</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -7178,11 +7178,11 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 10:45</t>
+          <t>2026-02-19 15:39</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7191,11 +7191,11 @@
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>85.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 13:49</t>
+          <t>2026-03-04 15:37</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -7204,11 +7204,11 @@
         </is>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>86</v>
+        <v>87.5</v>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:59</t>
+          <t>2026-03-19 20:22</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -7217,20 +7217,20 @@
         </is>
       </c>
       <c r="T61" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>438.5</v>
+        <v>419.4</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="X61" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>83.90000000000001</v>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
@@ -7257,85 +7257,85 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
+          <t>فريق 6</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:12</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 16:43</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 22:24</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06 04:47</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-20 04:40</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 13:06</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K62" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 01:02</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N62" s="3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 17:50</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:48</t>
-        </is>
-      </c>
-      <c r="S62" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q62" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 11:52</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T62" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>358.2</v>
+        <v>350.6</v>
       </c>
       <c r="V62" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W62" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
@@ -7366,28 +7366,28 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>فريق 2</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 21:54</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 4</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 21:42</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H63" s="3" t="n">
-        <v>76.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 18:38</t>
+          <t>2026-02-05 16:29</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -7396,11 +7396,11 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 17:41</t>
+          <t>2026-02-20 03:26</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -7409,11 +7409,11 @@
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>77.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 02:44</t>
+          <t>2026-03-05 18:44</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
@@ -7422,11 +7422,11 @@
         </is>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>78.2</v>
+        <v>82.5</v>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:48</t>
+          <t>2026-03-18 22:28</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
@@ -7435,16 +7435,16 @@
         </is>
       </c>
       <c r="T63" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>413.3</v>
+        <v>401</v>
       </c>
       <c r="V63" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W63" s="3" t="n">
-        <v>82.7</v>
+        <v>80.2</v>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
@@ -7475,67 +7475,67 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 19:06</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
+          <t>فريق 2</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 13:14</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 20:12</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H64" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 17:43</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K64" s="6" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="L64" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 22:42</t>
-        </is>
-      </c>
-      <c r="M64" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="N64" s="6" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="O64" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:18</t>
-        </is>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K64" s="3" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 03:46</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 23:58</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18 08:12</t>
+          <t>2026-03-19 00:48</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -7544,20 +7544,20 @@
         </is>
       </c>
       <c r="T64" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>347.3</v>
+        <v>417.8</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>69.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -7584,15 +7584,15 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>55.3</v>
+        <v>60</v>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 19:15</t>
+          <t>2026-01-23 22:24</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -7600,51 +7600,51 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H65" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 17:52</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 22:48</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="inlineStr">
+      <c r="H65" s="6" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 19:54</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="O65" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:25</t>
-        </is>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K65" s="3" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 18:53</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 16:16</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18 08:13</t>
+          <t>2026-03-20 15:02</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -7656,17 +7656,17 @@
         <v>0</v>
       </c>
       <c r="U65" s="3" t="n">
-        <v>347.3</v>
+        <v>372.1</v>
       </c>
       <c r="V65" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W65" s="3" t="n">
-        <v>69.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -7693,67 +7693,67 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 19:16</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
+          <t>فريق 5</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-23 19:55</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 19:41</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 18:12</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N66" s="6" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 11:48</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H66" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 17:52</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K66" s="6" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="L66" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 22:57</t>
-        </is>
-      </c>
-      <c r="M66" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="N66" s="6" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="O66" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:26</t>
-        </is>
-      </c>
-      <c r="P66" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
       <c r="Q66" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18 08:20</t>
+          <t>2026-03-19 13:27</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
@@ -7765,17 +7765,17 @@
         <v>0</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>347.3</v>
+        <v>376</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>69.5</v>
+        <v>75.2</v>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
@@ -7802,28 +7802,28 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>فريق 4</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 06:26</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 6</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H67" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 04:41</t>
+          <t>2026-02-06 05:01</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -7832,11 +7832,11 @@
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>81.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 20:40</t>
+          <t>2026-02-20 04:52</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -7844,43 +7844,43 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N67" s="3" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 15:39</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q67" s="6" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:12</t>
-        </is>
-      </c>
-      <c r="S67" s="6" t="inlineStr">
+      <c r="N67" s="6" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 13:20</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 11:54</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U67" s="3" t="n">
-        <v>374.6</v>
+        <v>350.6</v>
       </c>
       <c r="V67" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W67" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
@@ -7914,25 +7914,25 @@
           <t>فريق 4</t>
         </is>
       </c>
-      <c r="E68" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 06:27</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E68" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 21:57</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 04:49</t>
+          <t>2026-02-05 16:39</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -7941,11 +7941,11 @@
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>81.2</v>
+        <v>87</v>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 20:42</t>
+          <t>2026-02-20 03:41</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -7954,11 +7954,11 @@
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>77.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 15:54</t>
+          <t>2026-03-05 18:50</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
@@ -7966,34 +7966,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q68" s="6" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:16</t>
-        </is>
-      </c>
-      <c r="S68" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q68" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18 22:43</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T68" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>374.6</v>
+        <v>401</v>
       </c>
       <c r="V68" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W68" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
@@ -8020,28 +8020,28 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 16:53</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 1</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:33</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>53.3</v>
+        <v>63.7</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 22:35</t>
+          <t>2026-02-06 19:56</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
@@ -8050,11 +8050,11 @@
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>91.8</v>
+        <v>89.8</v>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 01:10</t>
+          <t>2026-02-19 19:00</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -8063,11 +8063,11 @@
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 18:04</t>
+          <t>2026-03-05 16:19</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -8075,30 +8075,30 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q69" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:50</t>
-        </is>
-      </c>
-      <c r="S69" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q69" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:17</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T69" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>358.2</v>
+        <v>372.1</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
@@ -8129,85 +8129,85 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
+          <t>فريق 6</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 16:47</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 22:28</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06 04:51</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-20 04:49</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N70" s="6" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 13:13</t>
+        </is>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K70" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 01:05</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N70" s="3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 17:55</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q70" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="R70" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:53</t>
-        </is>
-      </c>
-      <c r="S70" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q70" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 11:54</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>358.2</v>
+        <v>350.6</v>
       </c>
       <c r="V70" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
@@ -8238,41 +8238,41 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>فريق 2</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 22:06</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 18:43</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 1</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:37</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 20:07</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>86.8</v>
+        <v>89.8</v>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 17:55</t>
+          <t>2026-02-19 19:05</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
@@ -8281,11 +8281,11 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>77.5</v>
+        <v>78</v>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 02:56</t>
+          <t>2026-03-05 16:26</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
@@ -8294,11 +8294,11 @@
         </is>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>78.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 17:02</t>
+          <t>2026-03-20 15:09</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -8307,20 +8307,20 @@
         </is>
       </c>
       <c r="T71" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>413.3</v>
+        <v>372.1</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>82.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -8347,15 +8347,15 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>75</v>
+        <v>75.8</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 08:28</t>
+          <t>2026-01-23 20:04</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -8364,11 +8364,11 @@
         </is>
       </c>
       <c r="H72" s="3" t="n">
-        <v>69.8</v>
+        <v>77.3</v>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 05:10</t>
+          <t>2026-02-05 19:49</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -8377,11 +8377,11 @@
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>82.2</v>
+        <v>92.8</v>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 11:54</t>
+          <t>2026-02-19 18:15</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -8389,25 +8389,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N72" s="3" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 05:28</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N72" s="6" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 11:50</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>78.8</v>
+        <v>86.2</v>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 08:55</t>
+          <t>2026-03-19 13:31</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -8416,16 +8416,16 @@
         </is>
       </c>
       <c r="T72" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>395.4</v>
+        <v>376</v>
       </c>
       <c r="V72" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
@@ -8456,41 +8456,41 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>فريق 4</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 06:28</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 04:53</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 3</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 18:30</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 19:54</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>81.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 20:41</t>
+          <t>2026-02-20 08:10</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
@@ -8499,11 +8499,11 @@
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>77.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 15:51</t>
+          <t>2026-03-06 02:52</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -8511,34 +8511,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q73" s="6" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="R73" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:13</t>
-        </is>
-      </c>
-      <c r="S73" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q73" s="3" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:21</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T73" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>374.6</v>
+        <v>442.8</v>
       </c>
       <c r="V73" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W73" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="X73" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X73" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
@@ -8565,15 +8565,15 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>55.3</v>
+        <v>61</v>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 19:10</t>
+          <t>2026-01-23 21:43</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
@@ -8582,11 +8582,11 @@
         </is>
       </c>
       <c r="H74" s="3" t="n">
-        <v>79</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 17:53</t>
+          <t>2026-02-05 16:36</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -8594,38 +8594,38 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K74" s="6" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="L74" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 22:57</t>
-        </is>
-      </c>
-      <c r="M74" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="N74" s="6" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="O74" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:25</t>
-        </is>
-      </c>
-      <c r="P74" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K74" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-20 03:29</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 18:48</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18 08:14</t>
+          <t>2026-03-18 22:42</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -8634,20 +8634,20 @@
         </is>
       </c>
       <c r="T74" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>347.3</v>
+        <v>401</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>69.5</v>
+        <v>80.2</v>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -8674,15 +8674,15 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>فريق 6</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>86</v>
+        <v>75.8</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 13:38</t>
+          <t>2026-01-23 20:06</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -8691,11 +8691,11 @@
         </is>
       </c>
       <c r="H75" s="3" t="n">
-        <v>85.2</v>
+        <v>77.3</v>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 23:43</t>
+          <t>2026-02-05 19:44</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -8704,11 +8704,11 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 03:35</t>
+          <t>2026-02-19 18:25</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -8717,11 +8717,11 @@
         </is>
       </c>
       <c r="N75" s="6" t="n">
-        <v>68.3</v>
+        <v>43.9</v>
       </c>
       <c r="O75" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 22:54</t>
+          <t>2026-03-07 11:57</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
@@ -8730,11 +8730,11 @@
         </is>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>99</v>
+        <v>86.2</v>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:29</t>
+          <t>2026-03-19 13:41</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -8743,20 +8743,20 @@
         </is>
       </c>
       <c r="T75" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>463.5</v>
+        <v>376</v>
       </c>
       <c r="V75" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="X75" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>75.2</v>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -8783,28 +8783,28 @@
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 16:48</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 3</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 18:42</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>53.3</v>
+        <v>69</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 22:32</t>
+          <t>2026-02-06 20:00</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
@@ -8813,11 +8813,11 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>91.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 01:09</t>
+          <t>2026-02-20 08:19</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -8826,11 +8826,11 @@
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 17:58</t>
+          <t>2026-03-06 03:00</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -8838,34 +8838,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q76" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:54</t>
-        </is>
-      </c>
-      <c r="S76" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q76" s="3" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:32</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>358.2</v>
+        <v>442.8</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="X76" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X76" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
@@ -8892,41 +8892,41 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>فريق 4</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 06:35</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 04:54</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 3</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 18:34</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 19:59</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>81.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 20:47</t>
+          <t>2026-02-20 08:14</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -8935,11 +8935,11 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>77.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 15:45</t>
+          <t>2026-03-06 02:57</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
@@ -8947,34 +8947,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q77" s="6" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="R77" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 20:14</t>
-        </is>
-      </c>
-      <c r="S77" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q77" s="3" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:24</t>
+        </is>
+      </c>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T77" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>374.6</v>
+        <v>442.8</v>
       </c>
       <c r="V77" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W77" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="X77" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X77" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
@@ -9005,11 +9005,11 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>74.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 22:00</t>
+          <t>2026-01-22 13:15</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -9017,25 +9017,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="H78" s="3" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 18:40</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H78" s="6" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 20:27</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>86.8</v>
+        <v>94.2</v>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 17:44</t>
+          <t>2026-02-19 03:48</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -9044,11 +9044,11 @@
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>77.5</v>
+        <v>87.2</v>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 02:59</t>
+          <t>2026-03-06 00:12</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:50</t>
+          <t>2026-03-19 00:49</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
@@ -9073,13 +9073,13 @@
         <v>20</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>413.3</v>
+        <v>417.8</v>
       </c>
       <c r="V78" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W78" s="3" t="n">
-        <v>82.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
@@ -9110,15 +9110,15 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>فريق 6</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>86</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 13:46</t>
+          <t>2026-01-22 13:26</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -9126,25 +9126,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="H79" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 23:56</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H79" s="6" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 20:17</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 03:50</t>
+          <t>2026-02-19 03:54</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -9152,25 +9152,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N79" s="6" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="O79" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 22:57</t>
-        </is>
-      </c>
-      <c r="P79" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N79" s="3" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-06 00:03</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>99</v>
+        <v>78.3</v>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:32</t>
+          <t>2026-03-19 00:56</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
@@ -9179,20 +9179,20 @@
         </is>
       </c>
       <c r="T79" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>463.5</v>
+        <v>417.8</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="X79" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
+        <v>83.59999999999999</v>
+      </c>
+      <c r="X79" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -9219,28 +9219,28 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 08:34</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 6</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:19</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H80" s="3" t="n">
-        <v>69.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 05:19</t>
+          <t>2026-02-06 04:55</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -9249,11 +9249,11 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 12:09</t>
+          <t>2026-02-20 04:46</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -9261,25 +9261,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N80" s="3" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="O80" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 05:32</t>
-        </is>
-      </c>
-      <c r="P80" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N80" s="6" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 13:15</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>78.8</v>
+        <v>86.5</v>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 08:58</t>
+          <t>2026-03-19 12:05</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
@@ -9288,20 +9288,20 @@
         </is>
       </c>
       <c r="T80" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>395.4</v>
+        <v>350.6</v>
       </c>
       <c r="V80" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -9328,41 +9328,41 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 08:32</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 05:24</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 3</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-23 18:37</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-06 20:00</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>82.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 11:55</t>
+          <t>2026-02-20 08:12</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -9371,11 +9371,11 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 05:34</t>
+          <t>2026-03-06 02:58</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
@@ -9384,11 +9384,11 @@
         </is>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>78.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 08:57</t>
+          <t>2026-03-19 14:23</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -9397,20 +9397,20 @@
         </is>
       </c>
       <c r="T81" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>395.4</v>
+        <v>442.8</v>
       </c>
       <c r="V81" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W81" s="3" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="X81" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X81" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>لجين صالح</t>
+          <t>طالب STD-081</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -9441,11 +9441,11 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>64</v>
+        <v>63.2</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>2026-01-20 10:27</t>
+          <t>2026-01-20 11:09</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -9454,11 +9454,11 @@
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>69.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 16:31</t>
+          <t>2026-02-04 22:12</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -9509,13 +9509,13 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="n">
-        <v>133.7</v>
+        <v>132.3</v>
       </c>
       <c r="V82" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W82" s="11" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="X82" s="12" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>غادة نبيل</t>
+          <t>طالب STD-082</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -9550,11 +9550,11 @@
         </is>
       </c>
       <c r="E83" s="11" t="n">
-        <v>66.7</v>
+        <v>60.2</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>2026-01-20 20:44</t>
+          <t>2026-01-21 11:55</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -9563,11 +9563,11 @@
         </is>
       </c>
       <c r="H83" s="11" t="n">
-        <v>40.9</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>2026-02-06 20:55</t>
+          <t>2026-02-04 21:36</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
@@ -9618,13 +9618,13 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="n">
-        <v>107.6</v>
+        <v>127.8</v>
       </c>
       <c r="V83" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W83" s="11" t="n">
-        <v>21.5</v>
+        <v>25.6</v>
       </c>
       <c r="X83" s="12" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>رشا أنور</t>
+          <t>طالب STD-083</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -9659,11 +9659,11 @@
         </is>
       </c>
       <c r="E84" s="11" t="n">
-        <v>59.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>2026-01-19 09:47</t>
+          <t>2026-01-22 18:11</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -9672,11 +9672,11 @@
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>63.7</v>
+        <v>63.1</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>2026-02-02 09:45</t>
+          <t>2026-02-07 10:49</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -9727,13 +9727,13 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="n">
-        <v>123.4</v>
+        <v>130.5</v>
       </c>
       <c r="V84" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W84" s="11" t="n">
-        <v>24.7</v>
+        <v>26.1</v>
       </c>
       <c r="X84" s="12" t="inlineStr">
         <is>
@@ -9747,50 +9747,50 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="13" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>STD-084</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr">
-        <is>
-          <t>ميار حمدي</t>
-        </is>
-      </c>
-      <c r="C85" s="13" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>طالب STD-084</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
         <is>
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E85" s="14" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F85" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-24 09:42</t>
-        </is>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H85" s="14" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I85" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-07 17:54</t>
-        </is>
-      </c>
-      <c r="J85" s="14" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="E85" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-21 20:55</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-06 22:20</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K85" s="11" t="n">
@@ -9836,13 +9836,13 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="n">
-        <v>49.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="V85" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W85" s="11" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="X85" s="12" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>نيرة سامي</t>
+          <t>طالب STD-085</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -9877,11 +9877,11 @@
         </is>
       </c>
       <c r="E86" s="14" t="n">
-        <v>35.9</v>
+        <v>23.2</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 18:24</t>
+          <t>2026-01-23 21:42</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -9890,11 +9890,11 @@
         </is>
       </c>
       <c r="H86" s="14" t="n">
-        <v>37.6</v>
+        <v>25.6</v>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 22:00</t>
+          <t>2026-02-06 20:30</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
@@ -9945,13 +9945,13 @@
         <v>0</v>
       </c>
       <c r="U86" s="11" t="n">
-        <v>73.5</v>
+        <v>48.8</v>
       </c>
       <c r="V86" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W86" s="11" t="n">
-        <v>14.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X86" s="12" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>إيمان زكي</t>
+          <t>طالب STD-086</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 19:12</t>
+          <t>2026-01-24 17:54</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -9999,11 +9999,11 @@
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>18</v>
+        <v>41.5</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 20:54</t>
+          <t>2026-02-06 18:24</t>
         </is>
       </c>
       <c r="J87" s="14" t="inlineStr">
@@ -10054,13 +10054,13 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="n">
-        <v>40</v>
+        <v>63.5</v>
       </c>
       <c r="V87" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W87" s="11" t="n">
-        <v>8</v>
+        <v>12.7</v>
       </c>
       <c r="X87" s="12" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>أسماء حافظ</t>
+          <t>طالب STD-087</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -10095,11 +10095,11 @@
         </is>
       </c>
       <c r="E88" s="14" t="n">
-        <v>36.1</v>
+        <v>42.6</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 18:36</t>
+          <t>2026-01-23 22:12</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -10108,11 +10108,11 @@
         </is>
       </c>
       <c r="H88" s="14" t="n">
-        <v>35.7</v>
+        <v>43.8</v>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 21:48</t>
+          <t>2026-02-06 19:30</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
@@ -10163,13 +10163,13 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="n">
-        <v>71.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V88" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W88" s="11" t="n">
-        <v>14.4</v>
+        <v>17.3</v>
       </c>
       <c r="X88" s="12" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>دعاء رمضان</t>
+          <t>طالب STD-088</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -10204,11 +10204,11 @@
         </is>
       </c>
       <c r="E89" s="14" t="n">
-        <v>27.9</v>
+        <v>38.3</v>
       </c>
       <c r="F89" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 20:12</t>
+          <t>2026-01-23 21:18</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -10217,11 +10217,11 @@
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>48.9</v>
+        <v>35.9</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 18:54</t>
+          <t>2026-02-06 21:54</t>
         </is>
       </c>
       <c r="J89" s="14" t="inlineStr">
@@ -10272,13 +10272,13 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="n">
-        <v>76.8</v>
+        <v>74.2</v>
       </c>
       <c r="V89" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W89" s="11" t="n">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="X89" s="12" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>سلوى ممدوح</t>
+          <t>طالب STD-089</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -10313,11 +10313,11 @@
         </is>
       </c>
       <c r="E90" s="11" t="n">
-        <v>74.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22 13:22</t>
+          <t>2026-01-20 13:39</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>69.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>2026-02-03 13:57</t>
+          <t>2026-02-05 12:41</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
@@ -10381,13 +10381,13 @@
         <v>0</v>
       </c>
       <c r="U90" s="11" t="n">
-        <v>143.8</v>
+        <v>134.5</v>
       </c>
       <c r="V90" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W90" s="11" t="n">
-        <v>28.8</v>
+        <v>26.9</v>
       </c>
       <c r="X90" s="12" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>هند ماهر</t>
+          <t>طالب STD-090</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
@@ -10422,11 +10422,11 @@
         </is>
       </c>
       <c r="E91" s="11" t="n">
-        <v>78.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>2026-01-20 22:36</t>
+          <t>2026-01-21 13:11</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -10435,11 +10435,11 @@
         </is>
       </c>
       <c r="H91" s="11" t="n">
-        <v>74.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>2026-02-03 15:04</t>
+          <t>2026-02-05 17:06</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
@@ -10490,13 +10490,13 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="n">
-        <v>153.5</v>
+        <v>145.3</v>
       </c>
       <c r="V91" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W91" s="11" t="n">
-        <v>30.7</v>
+        <v>29.1</v>
       </c>
       <c r="X91" s="12" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>رانيا فريد</t>
+          <t>طالب STD-091</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -10527,15 +10527,15 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E92" s="11" t="n">
-        <v>80.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>2026-01-19 14:50</t>
+          <t>2026-01-22 11:11</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -10544,11 +10544,11 @@
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>77.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 19:36</t>
+          <t>2026-02-04 09:27</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
@@ -10599,13 +10599,13 @@
         <v>0</v>
       </c>
       <c r="U92" s="11" t="n">
-        <v>157.2</v>
+        <v>155.2</v>
       </c>
       <c r="V92" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W92" s="11" t="n">
-        <v>31.4</v>
+        <v>31</v>
       </c>
       <c r="X92" s="12" t="inlineStr">
         <is>
@@ -10619,32 +10619,32 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="inlineStr">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>STD-092</t>
         </is>
       </c>
-      <c r="B93" s="16" t="inlineStr">
-        <is>
-          <t>عزة طلعت</t>
-        </is>
-      </c>
-      <c r="C93" s="16" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="D93" s="16" t="inlineStr">
-        <is>
-          <t>فريق 6</t>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>طالب STD-092</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
-        <v>86</v>
+        <v>70.7</v>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>2026-01-23 13:50</t>
+          <t>2026-01-20 13:43</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -10653,11 +10653,11 @@
         </is>
       </c>
       <c r="H93" s="11" t="n">
-        <v>85.2</v>
+        <v>77</v>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 23:55</t>
+          <t>2026-02-04 10:04</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
@@ -10708,13 +10708,13 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="n">
-        <v>171.2</v>
+        <v>147.7</v>
       </c>
       <c r="V93" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W93" s="11" t="n">
-        <v>34.2</v>
+        <v>29.5</v>
       </c>
       <c r="X93" s="12" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>منار شوقي</t>
+          <t>طالب STD-093</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
@@ -10745,28 +10745,28 @@
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>فريق 1</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-23 08:34</t>
-        </is>
-      </c>
-      <c r="G94" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 4</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-23 21:51</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>69.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>2026-02-06 05:17</t>
+          <t>2026-02-05 16:30</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
@@ -10817,13 +10817,13 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="n">
-        <v>144.8</v>
+        <v>135.4</v>
       </c>
       <c r="V94" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W94" s="11" t="n">
-        <v>29</v>
+        <v>27.1</v>
       </c>
       <c r="X94" s="12" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>نادين عصام</t>
+          <t>طالب STD-094</t>
         </is>
       </c>
       <c r="C95" s="16" t="inlineStr">
@@ -10854,28 +10854,28 @@
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>فريق 7</t>
-        </is>
-      </c>
-      <c r="E95" s="14" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="F95" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-23 22:42</t>
-        </is>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>نعم</t>
+          <t>فريق 2</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-22 13:29</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="H95" s="14" t="n">
-        <v>28.2</v>
+        <v>66.2</v>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 19:54</t>
+          <t>2026-02-06 20:19</t>
         </is>
       </c>
       <c r="J95" s="14" t="inlineStr">
@@ -10926,13 +10926,13 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="n">
-        <v>56.6</v>
+        <v>138.1</v>
       </c>
       <c r="V95" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W95" s="11" t="n">
-        <v>11.3</v>
+        <v>27.6</v>
       </c>
       <c r="X95" s="12" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>شهد كمال</t>
+          <t>طالب STD-095</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
@@ -10963,15 +10963,15 @@
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E96" s="11" t="n">
-        <v>74.5</v>
+        <v>75.8</v>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22 22:07</t>
+          <t>2026-01-23 20:00</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
@@ -10980,11 +10980,11 @@
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>76.3</v>
+        <v>77.3</v>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 18:41</t>
+          <t>2026-02-05 19:55</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
@@ -11035,13 +11035,13 @@
         <v>0</v>
       </c>
       <c r="U96" s="11" t="n">
-        <v>150.8</v>
+        <v>153.1</v>
       </c>
       <c r="V96" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W96" s="11" t="n">
-        <v>30.2</v>
+        <v>30.6</v>
       </c>
       <c r="X96" s="12" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>فاطمة سعيد</t>
+          <t>طالب STD-096</t>
         </is>
       </c>
       <c r="C97" s="16" t="inlineStr">
@@ -11072,33 +11072,33 @@
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>فريق 6</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v>86</v>
-      </c>
-      <c r="F97" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-23 13:41</t>
-        </is>
-      </c>
-      <c r="G97" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H97" s="11" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>2026-02-05 23:55</t>
-        </is>
-      </c>
-      <c r="J97" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 1</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:36</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H97" s="14" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="I97" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-06 20:06</t>
+        </is>
+      </c>
+      <c r="J97" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K97" s="11" t="n">
@@ -11144,13 +11144,13 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="n">
-        <v>171.2</v>
+        <v>123.7</v>
       </c>
       <c r="V97" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W97" s="11" t="n">
-        <v>34.2</v>
+        <v>24.7</v>
       </c>
       <c r="X97" s="12" t="inlineStr">
         <is>
@@ -11265,31 +11265,31 @@
         </is>
       </c>
       <c r="C2" s="18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>20</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>70.84999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>71.38</v>
+        <v>72.95</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>67.36</v>
+        <v>64.25</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>66.73</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>65.56</v>
+        <v>62.33</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>344.92</v>
+        <v>335.04</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>0</v>
@@ -11307,34 +11307,34 @@
         </is>
       </c>
       <c r="C3" s="19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>20</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>51.92</v>
+        <v>51.72</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>56.75</v>
+        <v>58.55</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>53.1</v>
+        <v>56.12</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>52.18</v>
+        <v>53.55</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>48.38</v>
+        <v>51.2</v>
       </c>
       <c r="J3" s="19" t="n">
-        <v>268.14</v>
+        <v>277.18</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>53.63</v>
+        <v>55.44</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -11349,31 +11349,31 @@
         </is>
       </c>
       <c r="C4" s="20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="20" t="n">
         <v>20</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>75.13</v>
+        <v>72.45</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>74.59999999999999</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>79.13</v>
+        <v>74.05</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>72.90000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="I4" s="20" t="n">
-        <v>72.84999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>383.52</v>
+        <v>372.52</v>
       </c>
       <c r="K4" s="20" t="n">
-        <v>76.7</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="L4" s="20" t="n">
         <v>0</v>
@@ -11391,34 +11391,34 @@
         </is>
       </c>
       <c r="C5" s="21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>20</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>72.48</v>
+        <v>66.28</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>72.01000000000001</v>
+        <v>70.95</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>66.01000000000001</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>57.68</v>
+        <v>59.64</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>60.34</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="J5" s="21" t="n">
-        <v>334.72</v>
+        <v>351.02</v>
       </c>
       <c r="K5" s="21" t="n">
-        <v>66.95</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="L5" s="21" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/tasks_gradebook.xlsx
+++ b/tasks_gradebook.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 19:47</t>
+          <t>2026-03-06 20:47</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 20:27</t>
+          <t>2026-03-08 21:27</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 11:55</t>
+          <t>2026-03-11 15:55</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 14:49</t>
+          <t>2026-03-12 17:49</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 10:33</t>
+          <t>2026-03-12 18:13</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>54.2</v>
+        <v>61.7</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 15:53</t>
+          <t>2026-03-02 14:58</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 19:11</t>
+          <t>2026-03-05 20:46</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -856,11 +856,11 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>65.2</v>
+        <v>74.3</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 15:02</t>
+          <t>2026-03-05 17:28</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 19:40</t>
+          <t>2026-03-12 18:09</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -882,11 +882,11 @@
         </is>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>62.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:58</t>
+          <t>2026-03-12 22:44</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
@@ -898,17 +898,17 @@
         <v>0</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>316.6</v>
+        <v>326</v>
       </c>
       <c r="V3" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>63.3</v>
+        <v>65.2</v>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -939,11 +939,11 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>58</v>
+        <v>58.6</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 16:40</t>
+          <t>2026-03-08 20:28</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>58.2</v>
+        <v>60.3</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 11:49</t>
+          <t>2026-03-07 19:40</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -965,11 +965,11 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 10:18</t>
+          <t>2026-03-10 15:49</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -978,11 +978,11 @@
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 15:48</t>
+          <t>2026-03-10 14:18</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -991,11 +991,11 @@
         </is>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>67.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 21:17</t>
+          <t>2026-03-12 17:48</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1007,13 +1007,13 @@
         <v>0</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>332.2</v>
+        <v>327.9</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>66.8</v>
+        <v>62.6</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 15:42</t>
+          <t>2026-03-08 21:47</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 16:27</t>
+          <t>2026-03-09 18:42</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1074,11 +1074,11 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 09:08</t>
+          <t>2026-03-08 19:27</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -1087,11 +1087,11 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 15:40</t>
+          <t>2026-03-10 14:08</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -1100,11 +1100,11 @@
         </is>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:33</t>
+          <t>2026-03-12 17:40</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1116,13 +1116,13 @@
         <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>353</v>
+        <v>355.5</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>61.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 13:26</t>
+          <t>2026-03-09 21:18</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1170,11 +1170,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>68.7</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 12:24</t>
+          <t>2026-03-08 17:26</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1183,11 +1183,11 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>76.5</v>
+        <v>67.5</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 09:14</t>
+          <t>2026-03-11 16:24</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1196,11 +1196,11 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>78.5</v>
+        <v>74.2</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 20:16</t>
+          <t>2026-03-10 14:14</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>81</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 10:33</t>
+          <t>2026-03-12 21:16</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1225,17 +1225,17 @@
         <v>0</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>366.2</v>
+        <v>345.7</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>73.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 10:05</t>
+          <t>2026-03-02 17:48</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1279,11 +1279,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>75.8</v>
+        <v>76.3</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 18:27</t>
+          <t>2026-03-04 17:01</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 21:30</t>
+          <t>2026-03-05 20:43</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>80.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 15:41</t>
+          <t>2026-03-12 20:09</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1318,11 +1318,11 @@
         </is>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>71.8</v>
+        <v>83.3</v>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:22</t>
+          <t>2026-03-12 22:09</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1334,17 +1334,17 @@
         <v>0</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>367.7</v>
+        <v>376</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>73.5</v>
+        <v>75.2</v>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1375,11 +1375,11 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>65.2</v>
+        <v>70.2</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 14:54</t>
+          <t>2026-03-02 22:05</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1388,11 +1388,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>70.3</v>
+        <v>75.5</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 15:15</t>
+          <t>2026-03-04 17:57</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>56.8</v>
+        <v>72.3</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 12:46</t>
+          <t>2026-03-09 18:41</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1414,11 +1414,11 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>63.3</v>
+        <v>71.5</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 20:26</t>
+          <t>2026-03-10 20:58</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>63.9</v>
+        <v>75</v>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:05</t>
+          <t>2026-03-12 16:43</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1443,17 +1443,17 @@
         <v>0</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>319.5</v>
+        <v>364.5</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>63.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1484,11 +1484,11 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 15:51</t>
+          <t>2026-03-03 20:18</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>74.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 15:43</t>
+          <t>2026-03-08 18:10</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>53.1</v>
+        <v>60.7</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 13:37</t>
+          <t>2026-03-05 14:45</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1523,11 +1523,11 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>74.2</v>
+        <v>68</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 10:38</t>
+          <t>2026-03-11 19:25</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1536,11 +1536,11 @@
         </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>73.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 20:02</t>
+          <t>2026-03-12 15:35</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -1552,13 +1552,13 @@
         <v>0</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>340.7</v>
+        <v>336.7</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
@@ -1593,11 +1593,11 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 13:55</t>
+          <t>2026-03-07 19:08</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1606,11 +1606,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 15:20</t>
+          <t>2026-03-09 15:35</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1619,11 +1619,11 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>75.7</v>
+        <v>74</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 13:01</t>
+          <t>2026-03-08 16:55</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1632,11 +1632,11 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>85</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 14:28</t>
+          <t>2026-03-11 18:20</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>63.2</v>
+        <v>86</v>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 09:04</t>
+          <t>2026-03-12 16:01</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1661,17 +1661,17 @@
         <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>376.4</v>
+        <v>365.6</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>75.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -1702,11 +1702,11 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>81.7</v>
+        <v>62.1</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 22:19</t>
+          <t>2026-03-09 17:56</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1715,11 +1715,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>94.8</v>
+        <v>67.5</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 20:26</t>
+          <t>2026-03-04 18:28</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1728,11 +1728,11 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>81.7</v>
+        <v>80.7</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 14:49</t>
+          <t>2026-03-08 22:19</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1741,11 +1741,11 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>71.8</v>
+        <v>86.5</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 16:08</t>
+          <t>2026-03-10 21:26</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1754,11 +1754,11 @@
         </is>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>61.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:06</t>
+          <t>2026-03-12 17:49</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -1770,17 +1770,17 @@
         <v>5</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>396.7</v>
+        <v>400.4</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>79.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1811,11 +1811,11 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 22:13</t>
+          <t>2026-03-05 20:43</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1824,11 +1824,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:33</t>
+          <t>2026-03-05 16:06</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1837,11 +1837,11 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 13:49</t>
+          <t>2026-03-08 22:13</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1850,11 +1850,11 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 22:19</t>
+          <t>2026-03-10 15:33</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -1863,11 +1863,11 @@
         </is>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:17</t>
+          <t>2026-03-12 16:49</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -1876,20 +1876,20 @@
         </is>
       </c>
       <c r="T12" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>410.4</v>
+        <v>353.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -1920,11 +1920,11 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>70.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 11:53</t>
+          <t>2026-03-07 22:56</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1933,11 +1933,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02 20:53</t>
+          <t>2026-03-08 18:02</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1946,11 +1946,11 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>70.8</v>
+        <v>86.3</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 10:31</t>
+          <t>2026-03-05 22:59</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1959,11 +1959,11 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>82.3</v>
+        <v>81.8</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 09:46</t>
+          <t>2026-03-12 14:44</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>75.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:22</t>
+          <t>2026-03-12 16:53</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -1985,20 +1985,20 @@
         </is>
       </c>
       <c r="T13" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>374</v>
+        <v>396.2</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>74.8</v>
+        <v>79.2</v>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -2029,11 +2029,11 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 09:49</t>
+          <t>2026-03-02 20:44</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2042,11 +2042,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 19:10</t>
+          <t>2026-03-04 14:56</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -2055,11 +2055,11 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>80.3</v>
+        <v>80.7</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 19:52</t>
+          <t>2026-03-05 14:07</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -2068,11 +2068,11 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 12:18</t>
+          <t>2026-03-12 22:09</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2081,11 +2081,11 @@
         </is>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>68</v>
+        <v>90.2</v>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:58</t>
+          <t>2026-03-12 17:35</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -2094,20 +2094,20 @@
         </is>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>382.5</v>
+        <v>414.3</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>76.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2138,11 +2138,11 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 22:07</t>
+          <t>2026-03-05 22:00</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2151,11 +2151,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>75.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 21:41</t>
+          <t>2026-03-09 16:07</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2164,11 +2164,11 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 14:11</t>
+          <t>2026-03-10 22:07</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -2177,11 +2177,11 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 09:42</t>
+          <t>2026-03-11 22:41</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2190,11 +2190,11 @@
         </is>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>80.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:07</t>
+          <t>2026-03-12 17:11</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -2203,20 +2203,20 @@
         </is>
       </c>
       <c r="T15" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>407.8</v>
+        <v>379.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -2247,11 +2247,11 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 22:55</t>
+          <t>2026-03-05 15:29</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2260,11 +2260,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 17:33</t>
+          <t>2026-03-08 16:57</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>92.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 20:06</t>
+          <t>2026-03-09 22:55</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2286,11 +2286,11 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>88.7</v>
+        <v>84.7</v>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 19:25</t>
+          <t>2026-03-11 19:33</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2299,11 +2299,11 @@
         </is>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:35</t>
+          <t>2026-03-12 21:06</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2312,20 +2312,20 @@
         </is>
       </c>
       <c r="T16" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>443</v>
+        <v>399.3</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>79.90000000000001</v>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2356,11 +2356,11 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>71.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 13:49</t>
+          <t>2026-03-05 17:28</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2369,11 +2369,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>78</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 15:13</t>
+          <t>2026-03-05 21:01</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 19:36</t>
+          <t>2026-03-10 16:49</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -2395,11 +2395,11 @@
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 10:22</t>
+          <t>2026-03-10 18:13</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2408,11 +2408,11 @@
         </is>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:39</t>
+          <t>2026-03-12 20:36</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -2421,20 +2421,20 @@
         </is>
       </c>
       <c r="T17" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>391.6</v>
+        <v>451.3</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>90.3</v>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2465,11 +2465,11 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 22:06</t>
+          <t>2026-03-05 16:14</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2478,11 +2478,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 15:35</t>
+          <t>2026-03-04 21:48</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2491,11 +2491,11 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>100</v>
+        <v>81.2</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 11:49</t>
+          <t>2026-03-12 21:03</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2504,11 +2504,11 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 21:08</t>
+          <t>2026-03-10 17:08</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2517,11 +2517,11 @@
         </is>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>74.3</v>
+        <v>71</v>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:09</t>
+          <t>2026-03-12 16:18</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2533,17 +2533,17 @@
         <v>0</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>384.7</v>
+        <v>369.9</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -2574,11 +2574,11 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 20:03</t>
+          <t>2026-03-04 18:01</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2587,11 +2587,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>79.5</v>
+        <v>85.8</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03 16:40</t>
+          <t>2026-03-05 15:10</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2600,11 +2600,11 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 20:19</t>
+          <t>2026-03-08 17:35</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -2613,11 +2613,11 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>82.8</v>
+        <v>81.7</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 19:52</t>
+          <t>2026-03-12 21:23</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2626,11 +2626,11 @@
         </is>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>83.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 16:02</t>
+          <t>2026-03-12 22:30</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -2642,17 +2642,17 @@
         <v>5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>395</v>
+        <v>419.9</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 10:50</t>
+          <t>2026-03-09 22:24</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2696,11 +2696,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 14:55</t>
+          <t>2026-03-08 22:31</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2709,11 +2709,11 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>99.5</v>
+        <v>87.2</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 20:50</t>
+          <t>2026-03-05 14:50</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:58</t>
+          <t>2026-03-12 17:55</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -2735,11 +2735,11 @@
         </is>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>79.8</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:46</t>
+          <t>2026-03-12 21:50</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -2751,17 +2751,17 @@
         <v>15</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>456.5</v>
+        <v>441.6</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>91.3</v>
+        <v>88.3</v>
       </c>
       <c r="X20" s="4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>80.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 20:27</t>
+          <t>2026-03-05 20:08</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2805,11 +2805,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 18:38</t>
+          <t>2026-03-05 16:30</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2818,11 +2818,11 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>88.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 09:08</t>
+          <t>2026-03-10 21:27</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2831,11 +2831,11 @@
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>90</v>
+        <v>94.2</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 11:25</t>
+          <t>2026-03-11 20:38</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -2844,11 +2844,11 @@
         </is>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>94.7</v>
+        <v>93.8</v>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:22</t>
+          <t>2026-03-12 14:08</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -2860,17 +2860,17 @@
         <v>15</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>452.6</v>
+        <v>449</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>90.5</v>
+        <v>89.8</v>
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -2900,64 +2900,64 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 08:20</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 12:40</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 21:42</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-25 16:35</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="N22" s="6" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 22:12</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="H22" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-02 15:59</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
+      <c r="K22" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 06:04</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 11:00</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 06:09</t>
+          <t>2026-03-15 08:50</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -2969,13 +2969,13 @@
         <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>270.8</v>
+        <v>267.9</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>54.2</v>
+        <v>53.6</v>
       </c>
       <c r="X22" s="7" t="inlineStr">
         <is>
@@ -3010,11 +3010,11 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>44.9</v>
+        <v>39.1</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:18</t>
+          <t>2026-02-25 15:53</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -3023,11 +3023,11 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>27.1</v>
+        <v>47.6</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 18:24</t>
+          <t>2026-03-02 13:23</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -3036,11 +3036,11 @@
         </is>
       </c>
       <c r="K23" s="6" t="n">
-        <v>34.5</v>
+        <v>28.8</v>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>2026-02-20 21:48</t>
+          <t>2026-03-08 18:29</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -3049,11 +3049,11 @@
         </is>
       </c>
       <c r="N23" s="6" t="n">
-        <v>43.4</v>
+        <v>37.5</v>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 21:36</t>
+          <t>2026-03-11 12:47</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
@@ -3061,30 +3061,30 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="Q23" s="3" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:42</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="Q23" s="6" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:35</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>210.5</v>
+        <v>196.5</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>42.1</v>
+        <v>39.3</v>
       </c>
       <c r="X23" s="7" t="inlineStr">
         <is>
@@ -3119,11 +3119,11 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>59.9</v>
+        <v>56.8</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 05:35</t>
+          <t>2026-02-24 23:37</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -3132,11 +3132,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 19:49</t>
+          <t>2026-03-02 05:11</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3145,11 +3145,11 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>47.3</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 06:01</t>
+          <t>2026-03-08 02:50</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3157,47 +3157,47 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 03:30</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 22:24</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
+      <c r="N24" s="6" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:47</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-15 09:56</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T24" s="3" t="n">
         <v>10</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>307.3</v>
+        <v>296</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>61.5</v>
+        <v>59.2</v>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>44.7</v>
+        <v>47</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 21:30</t>
+          <t>2026-02-25 18:59</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -3240,51 +3240,51 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 23:20</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 21:00</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="H25" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-02 13:35</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="N25" s="6" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 20:54</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K25" s="3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 06:34</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 10:07</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>66.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 06:30</t>
+          <t>2026-03-15 03:14</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3296,17 +3296,17 @@
         <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>274</v>
+        <v>331.3</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="X25" s="7" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>66.3</v>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:18</t>
+          <t>2026-02-25 16:17</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 18:37</t>
+          <t>2026-03-02 17:44</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>2026-02-21 11:30</t>
+          <t>2026-03-09 11:29</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 05:51</t>
+          <t>2026-03-11 19:23</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 13:41</t>
+          <t>2026-03-15 07:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3446,11 +3446,11 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 05:43</t>
+          <t>2026-02-25 16:57</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>75</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 06:15</t>
+          <t>2026-03-02 11:37</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3472,11 +3472,11 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>74.2</v>
+        <v>77.2</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 20:31</t>
+          <t>2026-03-08 11:10</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -3485,11 +3485,11 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>71.8</v>
+        <v>74.8</v>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 20:32</t>
+          <t>2026-03-11 14:30</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3498,11 +3498,11 @@
         </is>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>28.1</v>
+        <v>31.4</v>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 21:06</t>
+          <t>2026-03-15 19:35</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
@@ -3514,13 +3514,13 @@
         <v>10</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>327</v>
+        <v>329.5</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
@@ -3555,11 +3555,11 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>55.2</v>
+        <v>64.5</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 22:50</t>
+          <t>2026-02-24 22:21</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3568,11 +3568,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:34</t>
+          <t>2026-03-02 12:23</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3581,11 +3581,11 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>87.5</v>
+        <v>73.8</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 00:44</t>
+          <t>2026-03-08 02:24</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -3594,11 +3594,11 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 14:05</t>
+          <t>2026-03-11 08:49</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -3607,11 +3607,11 @@
         </is>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:22</t>
+          <t>2026-03-15 00:53</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -3620,20 +3620,20 @@
         </is>
       </c>
       <c r="T28" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>377.6</v>
+        <v>365.1</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>75.5</v>
+        <v>73</v>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -3663,51 +3663,51 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-24 16:36</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="E29" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:29</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 05:56</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:05</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H29" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 18:24</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 11:52</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="N29" s="3" t="n">
-        <v>73.3</v>
+        <v>72.5</v>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 09:06</t>
+          <t>2026-03-11 10:31</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -3715,34 +3715,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 18:54</t>
-        </is>
-      </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q29" s="3" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-15 07:48</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T29" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>255.5</v>
+        <v>324.3</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="X29" s="7" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -3773,11 +3773,11 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>47.4</v>
+        <v>56.4</v>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 19:00</t>
+          <t>2026-02-25 20:53</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -3785,25 +3785,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H30" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 09:37</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H30" s="6" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-02 15:35</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>94.8</v>
+        <v>77.7</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 14:02</t>
+          <t>2026-03-08 03:06</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3812,11 +3812,11 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 04:11</t>
+          <t>2026-03-11 13:18</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -3825,11 +3825,11 @@
         </is>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>76.3</v>
+        <v>66.5</v>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 21:28</t>
+          <t>2026-03-15 06:41</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -3838,20 +3838,20 @@
         </is>
       </c>
       <c r="T30" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>389.3</v>
+        <v>321.2</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -3881,86 +3881,86 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 22:18</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="3" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 16:25</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 08:13</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 13:00</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:41</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H31" s="3" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 06:26</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 16:37</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 09:34</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 18:48</t>
-        </is>
-      </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q31" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-15 03:48</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T31" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>311</v>
+        <v>378.9</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>62.2</v>
+        <v>75.8</v>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -3991,11 +3991,11 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>72.5</v>
+        <v>79</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 16:52</t>
+          <t>2026-02-25 09:27</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4004,11 +4004,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 06:01</t>
+          <t>2026-03-01 16:56</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4017,11 +4017,11 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>60.5</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 22:30</t>
+          <t>2026-03-08 01:35</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -4030,11 +4030,11 @@
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 16:13</t>
+          <t>2026-03-11 05:42</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4043,11 +4043,11 @@
         </is>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>78</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18 20:03</t>
+          <t>2026-03-15 00:09</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -4059,17 +4059,17 @@
         <v>20</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>416.8</v>
+        <v>381.1</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -4100,11 +4100,11 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 15:24</t>
+          <t>2026-02-25 14:23</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -4113,11 +4113,11 @@
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>27.4</v>
+        <v>50.2</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 21:06</t>
+          <t>2026-03-02 18:11</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
@@ -4125,60 +4125,60 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="K33" s="6" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 19:00</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:30</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 19:24</t>
-        </is>
-      </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K33" s="3" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 10:54</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 10:05</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-15 03:28</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T33" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>223.1</v>
+        <v>377.2</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="X33" s="7" t="inlineStr">
-        <is>
-          <t>F</t>
+        <v>75.40000000000001</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -4209,11 +4209,11 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>83.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 08:55</t>
+          <t>2026-02-25 08:25</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -4222,11 +4222,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>85.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 17:23</t>
+          <t>2026-03-02 04:58</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4235,11 +4235,11 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 22:03</t>
+          <t>2026-03-08 09:47</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -4248,11 +4248,11 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>80.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 07:49</t>
+          <t>2026-03-11 00:23</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4260,34 +4260,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 22:48</t>
-        </is>
-      </c>
-      <c r="S34" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q34" s="3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-15 00:12</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T34" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>366.9</v>
+        <v>398.4</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -4317,25 +4317,25 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 06:42</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E35" s="6" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-25 21:05</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>54.1</v>
+        <v>62.8</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 21:48</t>
+          <t>2026-03-02 17:05</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -4343,60 +4343,60 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="K35" s="6" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 20:06</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 18:54</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 21:30</t>
-        </is>
-      </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K35" s="3" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 13:21</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:09</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-15 08:49</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>293.2</v>
+        <v>345.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>58.6</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -4426,64 +4426,64 @@
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 04:32</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 22:11</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 07:30</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 17:06</t>
-        </is>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
+      <c r="E36" s="6" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:17</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
+      <c r="H36" s="6" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-02 16:53</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:05</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:21</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
       <c r="Q36" s="3" t="n">
-        <v>89.3</v>
+        <v>81.8</v>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 18:19</t>
+          <t>2026-03-15 14:17</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -4492,20 +4492,20 @@
         </is>
       </c>
       <c r="T36" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>369</v>
+        <v>315.7</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>73.8</v>
+        <v>63.1</v>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>D+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -4536,11 +4536,11 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>47.8</v>
+        <v>54.5</v>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 20:30</t>
+          <t>2026-02-25 16:23</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -4549,11 +4549,11 @@
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>53.7</v>
+        <v>56.1</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 22:06</t>
+          <t>2026-03-02 18:29</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -4561,25 +4561,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="K37" s="3" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 10:38</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K37" s="6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-09 15:17</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N37" s="6" t="n">
-        <v>60.5</v>
+        <v>53.6</v>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 22:36</t>
+          <t>2026-03-11 18:59</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
@@ -4588,11 +4588,11 @@
         </is>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>51.6</v>
+        <v>45.8</v>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 22:24</t>
+          <t>2026-03-15 17:11</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
@@ -4604,17 +4604,17 @@
         <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>282.1</v>
+        <v>240.3</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
+        <v>48.1</v>
+      </c>
+      <c r="X37" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -4645,11 +4645,11 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>54.9</v>
+        <v>51.4</v>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 22:18</t>
+          <t>2026-02-25 15:29</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -4658,11 +4658,11 @@
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>29.9</v>
+        <v>32.3</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>2026-02-07 15:18</t>
+          <t>2026-03-02 23:17</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
@@ -4671,11 +4671,11 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>73.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 12:42</t>
+          <t>2026-03-08 08:52</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4684,11 +4684,11 @@
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>64.5</v>
+        <v>72.2</v>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 08:55</t>
+          <t>2026-03-11 06:55</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -4697,11 +4697,11 @@
         </is>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>90.3</v>
+        <v>81</v>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:17</t>
+          <t>2026-03-15 10:58</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="T38" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>322.8</v>
+        <v>317.5</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
@@ -4754,11 +4754,11 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>26.8</v>
+        <v>55.4</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36</t>
+          <t>2026-02-25 15:23</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -4766,38 +4766,38 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 16:12</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 03:53</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H39" s="6" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-02 13:59</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:11</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N39" s="6" t="n">
-        <v>58.5</v>
+        <v>46.3</v>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06 22:24</t>
+          <t>2026-03-11 17:17</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
@@ -4805,30 +4805,30 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-20 19:06</t>
-        </is>
-      </c>
-      <c r="S39" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q39" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:59</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>293.1</v>
+        <v>282.6</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>58.6</v>
+        <v>56.5</v>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
@@ -4863,11 +4863,11 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>52.2</v>
+        <v>32.6</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 21:36</t>
+          <t>2026-02-26 09:59</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -4875,38 +4875,38 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 19:06</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 17:26</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H40" s="6" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-02 13:17</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-08 14:41</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 01:26</t>
+          <t>2026-03-11 04:54</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -4915,11 +4915,11 @@
         </is>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>52.4</v>
+        <v>30</v>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20 21:24</t>
+          <t>2026-03-16 11:23</t>
         </is>
       </c>
       <c r="S40" s="6" t="inlineStr">
@@ -4928,20 +4928,20 @@
         </is>
       </c>
       <c r="T40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>369.4</v>
+        <v>262.1</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>52.4</v>
+      </c>
+      <c r="X40" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -4972,11 +4972,11 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>82.8</v>
+        <v>80</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 06:59</t>
+          <t>2026-02-25 05:21</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -4985,11 +4985,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>87.8</v>
+        <v>77.3</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 20:50</t>
+          <t>2026-03-02 07:02</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4997,25 +4997,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K41" s="6" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-20 22:24</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="K41" s="3" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-07 20:18</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>99</v>
+        <v>81.5</v>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 08:37</t>
+          <t>2026-03-11 05:44</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
@@ -5024,11 +5024,11 @@
         </is>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>89</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 15:30</t>
+          <t>2026-03-15 05:42</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -5040,17 +5040,17 @@
         <v>20</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>435.3</v>
+        <v>415.5</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="X41" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5081,11 +5081,11 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>63.9</v>
+        <v>66</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 13:31</t>
+          <t>2026-03-04 18:11</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5094,11 +5094,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 12:35</t>
+          <t>2026-03-05 16:06</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5107,11 +5107,11 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 09:17</t>
+          <t>2026-03-08 16:57</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5120,11 +5120,11 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 13:19</t>
+          <t>2026-03-12 22:25</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -5133,11 +5133,11 @@
         </is>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:52</t>
+          <t>2026-03-12 22:57</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -5149,17 +5149,17 @@
         <v>0</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>361.6</v>
+        <v>388.3</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>72.3</v>
+        <v>77.7</v>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5190,11 +5190,11 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 22:59</t>
+          <t>2026-03-07 21:18</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5203,11 +5203,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 12:48</t>
+          <t>2026-03-05 21:06</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5216,11 +5216,11 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>92.8</v>
+        <v>78.2</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:47</t>
+          <t>2026-03-09 20:03</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5229,11 +5229,11 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 11:33</t>
+          <t>2026-03-10 18:12</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5242,11 +5242,11 @@
         </is>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:39</t>
+          <t>2026-03-12 18:23</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -5255,20 +5255,20 @@
         </is>
       </c>
       <c r="T43" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>442.3</v>
+        <v>389.2</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="X43" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>77.8</v>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -5299,11 +5299,11 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>69.2</v>
+        <v>72.2</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 13:02</t>
+          <t>2026-03-04 16:29</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -5312,11 +5312,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 17:03</t>
+          <t>2026-03-03 17:25</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5325,11 +5325,11 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:30</t>
+          <t>2026-03-08 18:50</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -5338,11 +5338,11 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>84.7</v>
+        <v>76.8</v>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 09:03</t>
+          <t>2026-03-11 16:19</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5351,11 +5351,11 @@
         </is>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:23</t>
+          <t>2026-03-12 22:28</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -5367,13 +5367,13 @@
         <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>387.1</v>
+        <v>396.2</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
@@ -5408,11 +5408,11 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>63.9</v>
+        <v>66</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 13:43</t>
+          <t>2026-03-04 18:24</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -5421,11 +5421,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 12:36</t>
+          <t>2026-03-05 16:17</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -5434,11 +5434,11 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 09:31</t>
+          <t>2026-03-08 17:03</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -5447,11 +5447,11 @@
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 13:30</t>
+          <t>2026-03-12 22:29</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:59</t>
+          <t>2026-03-12 23:09</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -5476,17 +5476,17 @@
         <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>361.6</v>
+        <v>388.3</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>72.3</v>
+        <v>77.7</v>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -5517,11 +5517,11 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>77</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 11:09</t>
+          <t>2026-03-08 16:01</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -5530,11 +5530,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>78.2</v>
+        <v>75</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 09:16</t>
+          <t>2026-03-05 22:55</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5543,11 +5543,11 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>93.3</v>
+        <v>83.8</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 15:24</t>
+          <t>2026-03-10 15:09</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5556,11 +5556,11 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 15:28</t>
+          <t>2026-03-08 14:28</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -5569,11 +5569,11 @@
         </is>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>87.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:13</t>
+          <t>2026-03-12 16:13</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -5582,16 +5582,16 @@
         </is>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>419.4</v>
+        <v>421.3</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
@@ -5626,11 +5626,11 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>70.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 13:28</t>
+          <t>2026-03-04 19:59</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -5639,11 +5639,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>77</v>
+        <v>82.5</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 09:51</t>
+          <t>2026-03-05 21:14</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5652,11 +5652,11 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 18:36</t>
+          <t>2026-03-05 22:58</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -5665,11 +5665,11 @@
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>94.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:01</t>
+          <t>2026-03-12 19:04</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -5678,11 +5678,11 @@
         </is>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 21:55</t>
+          <t>2026-03-12 17:08</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -5691,20 +5691,20 @@
         </is>
       </c>
       <c r="T47" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>447.6</v>
+        <v>461.5</v>
       </c>
       <c r="V47" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W47" s="3" t="n">
-        <v>89.5</v>
+        <v>92.3</v>
       </c>
       <c r="X47" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -5735,11 +5735,11 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>69.2</v>
+        <v>72.2</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 13:05</t>
+          <t>2026-03-04 16:34</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5748,11 +5748,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 17:16</t>
+          <t>2026-03-03 17:34</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5761,11 +5761,11 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:31</t>
+          <t>2026-03-08 19:02</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -5774,11 +5774,11 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>84.7</v>
+        <v>76.8</v>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 09:06</t>
+          <t>2026-03-11 16:21</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -5787,11 +5787,11 @@
         </is>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:25</t>
+          <t>2026-03-12 22:38</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -5803,13 +5803,13 @@
         <v>0</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>387.1</v>
+        <v>396.2</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W48" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
@@ -5844,11 +5844,11 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>77</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 11:20</t>
+          <t>2026-03-08 16:06</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5857,11 +5857,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>78.2</v>
+        <v>75</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 09:26</t>
+          <t>2026-03-05 22:59</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5870,11 +5870,11 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>93.3</v>
+        <v>83.8</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 15:32</t>
+          <t>2026-03-10 15:17</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -5883,11 +5883,11 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 15:32</t>
+          <t>2026-03-08 14:35</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5896,11 +5896,11 @@
         </is>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>87.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:15</t>
+          <t>2026-03-12 16:23</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -5909,16 +5909,16 @@
         </is>
       </c>
       <c r="T49" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>419.4</v>
+        <v>421.3</v>
       </c>
       <c r="V49" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
@@ -5953,11 +5953,11 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>63.9</v>
+        <v>66</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 13:40</t>
+          <t>2026-03-04 18:16</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5966,11 +5966,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 12:39</t>
+          <t>2026-03-05 16:19</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5979,11 +5979,11 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 09:26</t>
+          <t>2026-03-08 16:59</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -5992,11 +5992,11 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 13:30</t>
+          <t>2026-03-12 22:38</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -6005,11 +6005,11 @@
         </is>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:05</t>
+          <t>2026-03-12 22:58</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -6021,17 +6021,17 @@
         <v>0</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>361.6</v>
+        <v>388.3</v>
       </c>
       <c r="V50" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W50" s="3" t="n">
-        <v>72.3</v>
+        <v>77.7</v>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -6062,11 +6062,11 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>69.2</v>
+        <v>72.2</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 13:10</t>
+          <t>2026-03-04 16:41</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -6075,11 +6075,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 17:04</t>
+          <t>2026-03-03 17:31</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -6088,11 +6088,11 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:35</t>
+          <t>2026-03-08 18:56</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -6101,11 +6101,11 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>84.7</v>
+        <v>76.8</v>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16</t>
+          <t>2026-03-11 16:20</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -6114,11 +6114,11 @@
         </is>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:31</t>
+          <t>2026-03-12 22:39</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -6130,13 +6130,13 @@
         <v>0</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>387.1</v>
+        <v>396.2</v>
       </c>
       <c r="V51" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
@@ -6171,11 +6171,11 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>78.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 17:58</t>
+          <t>2026-03-08 15:14</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -6184,11 +6184,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02 17:04</t>
+          <t>2026-03-05 15:40</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -6197,11 +6197,11 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 14:08</t>
+          <t>2026-03-09 20:47</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:06</t>
+          <t>2026-03-09 18:15</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -6223,11 +6223,11 @@
         </is>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:30</t>
+          <t>2026-03-12 14:33</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -6236,20 +6236,20 @@
         </is>
       </c>
       <c r="T52" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>435.4</v>
+        <v>466.8</v>
       </c>
       <c r="V52" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W52" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="X52" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -6280,11 +6280,11 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>78.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 18:05</t>
+          <t>2026-03-08 15:29</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -6293,11 +6293,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02 17:14</t>
+          <t>2026-03-05 15:49</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 14:13</t>
+          <t>2026-03-09 20:56</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6319,11 +6319,11 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:19</t>
+          <t>2026-03-09 18:21</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -6332,11 +6332,11 @@
         </is>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:32</t>
+          <t>2026-03-12 14:35</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -6345,20 +6345,20 @@
         </is>
       </c>
       <c r="T53" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>435.4</v>
+        <v>466.8</v>
       </c>
       <c r="V53" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W53" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="X53" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -6389,11 +6389,11 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 23:12</t>
+          <t>2026-03-07 21:27</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -6402,11 +6402,11 @@
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 12:49</t>
+          <t>2026-03-05 21:20</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -6415,11 +6415,11 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>92.8</v>
+        <v>78.2</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:59</t>
+          <t>2026-03-09 20:05</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6428,11 +6428,11 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 11:39</t>
+          <t>2026-03-10 18:26</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -6441,11 +6441,11 @@
         </is>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:45</t>
+          <t>2026-03-12 18:30</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -6454,20 +6454,20 @@
         </is>
       </c>
       <c r="T54" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>442.3</v>
+        <v>389.2</v>
       </c>
       <c r="V54" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="X54" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>77.8</v>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
@@ -6498,11 +6498,11 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>78.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 17:59</t>
+          <t>2026-03-08 15:23</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -6511,11 +6511,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02 17:15</t>
+          <t>2026-03-05 15:43</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -6524,11 +6524,11 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 14:11</t>
+          <t>2026-03-09 20:57</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6537,11 +6537,11 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:16</t>
+          <t>2026-03-09 18:18</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -6550,11 +6550,11 @@
         </is>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:41</t>
+          <t>2026-03-12 14:38</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -6563,20 +6563,20 @@
         </is>
       </c>
       <c r="T55" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>435.4</v>
+        <v>466.8</v>
       </c>
       <c r="V55" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="X55" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
@@ -6607,11 +6607,11 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 23:12</t>
+          <t>2026-03-07 21:29</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -6620,11 +6620,11 @@
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 12:59</t>
+          <t>2026-03-05 21:07</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6633,11 +6633,11 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>92.8</v>
+        <v>78.2</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:52</t>
+          <t>2026-03-09 20:10</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6646,11 +6646,11 @@
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 11:45</t>
+          <t>2026-03-10 18:21</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -6659,11 +6659,11 @@
         </is>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:52</t>
+          <t>2026-03-12 18:25</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -6672,20 +6672,20 @@
         </is>
       </c>
       <c r="T56" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>442.3</v>
+        <v>389.2</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="X56" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>77.8</v>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
@@ -6716,11 +6716,11 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>70.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 13:33</t>
+          <t>2026-03-04 20:04</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -6729,11 +6729,11 @@
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>77</v>
+        <v>82.5</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 09:53</t>
+          <t>2026-03-05 21:20</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6742,11 +6742,11 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 18:50</t>
+          <t>2026-03-05 23:08</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -6755,11 +6755,11 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>94.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:04</t>
+          <t>2026-03-12 19:19</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -6768,11 +6768,11 @@
         </is>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 22:04</t>
+          <t>2026-03-12 17:21</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -6781,20 +6781,20 @@
         </is>
       </c>
       <c r="T57" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>447.6</v>
+        <v>461.5</v>
       </c>
       <c r="V57" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W57" s="3" t="n">
-        <v>89.5</v>
+        <v>92.3</v>
       </c>
       <c r="X57" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -6825,11 +6825,11 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 23:03</t>
+          <t>2026-03-07 21:21</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6838,11 +6838,11 @@
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 12:50</t>
+          <t>2026-03-05 21:07</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6851,11 +6851,11 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>92.8</v>
+        <v>78.2</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 12:59</t>
+          <t>2026-03-09 20:04</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -6864,11 +6864,11 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 11:36</t>
+          <t>2026-03-10 18:21</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -6877,11 +6877,11 @@
         </is>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:50</t>
+          <t>2026-03-12 18:26</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -6890,20 +6890,20 @@
         </is>
       </c>
       <c r="T58" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>442.3</v>
+        <v>389.2</v>
       </c>
       <c r="V58" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W58" s="3" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="X58" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>77.8</v>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -6934,11 +6934,11 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>78.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 18:09</t>
+          <t>2026-03-08 15:18</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -6947,11 +6947,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02 17:05</t>
+          <t>2026-03-05 15:53</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 14:11</t>
+          <t>2026-03-09 21:01</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -6973,11 +6973,11 @@
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:18</t>
+          <t>2026-03-09 18:28</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -6986,11 +6986,11 @@
         </is>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:38</t>
+          <t>2026-03-12 14:37</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -6999,20 +6999,20 @@
         </is>
       </c>
       <c r="T59" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>435.4</v>
+        <v>466.8</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="X59" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -7043,11 +7043,11 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>70.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 13:30</t>
+          <t>2026-03-04 20:09</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -7056,11 +7056,11 @@
         </is>
       </c>
       <c r="H60" s="3" t="n">
-        <v>77</v>
+        <v>82.5</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:06</t>
+          <t>2026-03-05 21:24</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -7069,11 +7069,11 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 18:40</t>
+          <t>2026-03-05 23:01</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -7082,11 +7082,11 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>94.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:02</t>
+          <t>2026-03-12 19:13</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -7095,11 +7095,11 @@
         </is>
       </c>
       <c r="Q60" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 22:09</t>
+          <t>2026-03-12 17:16</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -7108,20 +7108,20 @@
         </is>
       </c>
       <c r="T60" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>447.6</v>
+        <v>461.5</v>
       </c>
       <c r="V60" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W60" s="3" t="n">
-        <v>89.5</v>
+        <v>92.3</v>
       </c>
       <c r="X60" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -7152,11 +7152,11 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>77</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 11:10</t>
+          <t>2026-03-08 16:07</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -7165,11 +7165,11 @@
         </is>
       </c>
       <c r="H61" s="3" t="n">
-        <v>78.2</v>
+        <v>75</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 09:25</t>
+          <t>2026-03-05 23:07</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -7178,11 +7178,11 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>93.3</v>
+        <v>83.8</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 15:39</t>
+          <t>2026-03-10 15:20</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7191,11 +7191,11 @@
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 15:37</t>
+          <t>2026-03-08 14:36</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -7204,11 +7204,11 @@
         </is>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>87.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 20:22</t>
+          <t>2026-03-12 16:24</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -7217,16 +7217,16 @@
         </is>
       </c>
       <c r="T61" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>419.4</v>
+        <v>421.3</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
@@ -7260,38 +7260,38 @@
           <t>فريق 6</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 22:12</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="E62" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 04:38</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:35</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H62" s="3" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 04:47</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="K62" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 04:40</t>
+          <t>2026-03-08 14:42</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7299,25 +7299,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N62" s="6" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="O62" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 13:06</t>
-        </is>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N62" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 18:38</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q62" s="3" t="n">
-        <v>86.5</v>
+        <v>83</v>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:52</t>
+          <t>2026-03-15 16:57</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
@@ -7329,13 +7329,13 @@
         <v>0</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>350.6</v>
+        <v>369.1</v>
       </c>
       <c r="V62" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W62" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
@@ -7369,86 +7369,86 @@
           <t>فريق 4</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 21:42</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="E63" s="3" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:32</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:49</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 08:28</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 06:17</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:47</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H63" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 16:29</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 03:26</t>
-        </is>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 18:44</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q63" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="R63" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-18 22:28</t>
-        </is>
-      </c>
-      <c r="S63" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="T63" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>401</v>
+        <v>369.3</v>
       </c>
       <c r="V63" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W63" s="3" t="n">
-        <v>80.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
@@ -7478,25 +7478,25 @@
           <t>فريق 2</t>
         </is>
       </c>
-      <c r="E64" s="3" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 13:14</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E64" s="6" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-25 19:11</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H64" s="6" t="n">
-        <v>66.2</v>
+        <v>64</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 20:12</t>
+          <t>2026-03-02 17:35</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
@@ -7504,25 +7504,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="K64" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 03:46</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K64" s="6" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-08 16:35</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>87.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 23:58</t>
+          <t>2026-03-11 10:35</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -7531,11 +7531,11 @@
         </is>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>78.3</v>
+        <v>83.5</v>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 00:48</t>
+          <t>2026-03-15 09:29</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -7544,20 +7544,20 @@
         </is>
       </c>
       <c r="T64" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>417.8</v>
+        <v>343.8</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -7588,11 +7588,11 @@
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>60</v>
+        <v>58.2</v>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 22:24</t>
+          <t>2026-02-25 19:59</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -7600,25 +7600,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H65" s="6" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 19:54</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H65" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 12:32</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>89.8</v>
+        <v>86.7</v>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 18:53</t>
+          <t>2026-03-08 09:58</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -7627,11 +7627,11 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>78</v>
+        <v>79.7</v>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 16:16</t>
+          <t>2026-03-11 05:30</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -7640,11 +7640,11 @@
         </is>
       </c>
       <c r="Q65" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:02</t>
+          <t>2026-03-15 15:22</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -7653,20 +7653,20 @@
         </is>
       </c>
       <c r="T65" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U65" s="3" t="n">
-        <v>372.1</v>
+        <v>393</v>
       </c>
       <c r="V65" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W65" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -7697,11 +7697,11 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>75.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 19:55</t>
+          <t>2026-02-25 09:45</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="H66" s="3" t="n">
-        <v>77.3</v>
+        <v>81.8</v>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 19:41</t>
+          <t>2026-03-02 17:26</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -7723,11 +7723,11 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>92.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 18:12</t>
+          <t>2026-03-08 06:02</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -7735,25 +7735,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N66" s="6" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="O66" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 11:48</t>
-        </is>
-      </c>
-      <c r="P66" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N66" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 06:16</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>86.2</v>
+        <v>87.7</v>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:27</t>
+          <t>2026-03-15 06:56</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
@@ -7762,20 +7762,20 @@
         </is>
       </c>
       <c r="T66" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>376</v>
+        <v>419.7</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>75.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
@@ -7805,38 +7805,38 @@
           <t>فريق 6</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 22:17</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="E67" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 04:39</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:39</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H67" s="3" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 05:01</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="K67" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 04:52</t>
+          <t>2026-03-08 14:52</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -7844,25 +7844,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="O67" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 13:20</t>
-        </is>
-      </c>
-      <c r="P67" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N67" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 18:53</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>86.5</v>
+        <v>83</v>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:54</t>
+          <t>2026-03-15 17:04</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -7874,13 +7874,13 @@
         <v>0</v>
       </c>
       <c r="U67" s="3" t="n">
-        <v>350.6</v>
+        <v>369.1</v>
       </c>
       <c r="V67" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W67" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
@@ -7914,86 +7914,86 @@
           <t>فريق 4</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 21:57</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="E68" s="3" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:34</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:53</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 08:42</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 06:28</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:49</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H68" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 16:39</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 03:41</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N68" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 18:50</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q68" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="R68" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-18 22:43</t>
-        </is>
-      </c>
-      <c r="S68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="T68" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>401</v>
+        <v>369.3</v>
       </c>
       <c r="V68" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W68" s="3" t="n">
-        <v>80.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
@@ -8024,11 +8024,11 @@
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>60</v>
+        <v>58.2</v>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 22:33</t>
+          <t>2026-02-25 20:05</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -8036,25 +8036,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H69" s="6" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 19:56</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H69" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 12:36</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>89.8</v>
+        <v>86.7</v>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 19:00</t>
+          <t>2026-03-08 10:01</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -8063,11 +8063,11 @@
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>78</v>
+        <v>79.7</v>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 16:19</t>
+          <t>2026-03-11 05:43</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -8076,11 +8076,11 @@
         </is>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:17</t>
+          <t>2026-03-15 15:32</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
@@ -8089,20 +8089,20 @@
         </is>
       </c>
       <c r="T69" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>372.1</v>
+        <v>393</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
@@ -8132,38 +8132,38 @@
           <t>فريق 6</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 22:17</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="E70" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 04:41</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:45</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H70" s="3" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 04:51</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="K70" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 04:49</t>
+          <t>2026-03-08 14:49</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -8171,25 +8171,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N70" s="6" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="O70" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 13:13</t>
-        </is>
-      </c>
-      <c r="P70" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N70" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 18:39</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>86.5</v>
+        <v>83</v>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 11:54</t>
+          <t>2026-03-15 17:04</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -8201,13 +8201,13 @@
         <v>0</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>350.6</v>
+        <v>369.1</v>
       </c>
       <c r="V70" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
@@ -8242,11 +8242,11 @@
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>60</v>
+        <v>58.2</v>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 22:37</t>
+          <t>2026-02-25 20:02</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -8254,25 +8254,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H71" s="6" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 20:07</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H71" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 12:36</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>89.8</v>
+        <v>86.7</v>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 19:05</t>
+          <t>2026-03-08 10:12</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
@@ -8281,11 +8281,11 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>78</v>
+        <v>79.7</v>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 16:26</t>
+          <t>2026-03-11 05:41</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
@@ -8294,11 +8294,11 @@
         </is>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:09</t>
+          <t>2026-03-15 15:25</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -8307,20 +8307,20 @@
         </is>
       </c>
       <c r="T71" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>372.1</v>
+        <v>393</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -8351,11 +8351,11 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>75.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 20:04</t>
+          <t>2026-02-25 09:58</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -8364,11 +8364,11 @@
         </is>
       </c>
       <c r="H72" s="3" t="n">
-        <v>77.3</v>
+        <v>81.8</v>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 19:49</t>
+          <t>2026-03-02 17:35</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -8377,11 +8377,11 @@
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>92.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 18:15</t>
+          <t>2026-03-08 06:16</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -8389,25 +8389,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N72" s="6" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 11:50</t>
-        </is>
-      </c>
-      <c r="P72" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N72" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 06:28</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>86.2</v>
+        <v>87.7</v>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:31</t>
+          <t>2026-03-15 07:02</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -8416,20 +8416,20 @@
         </is>
       </c>
       <c r="T72" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>376</v>
+        <v>419.7</v>
       </c>
       <c r="V72" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>75.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>67.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:30</t>
+          <t>2026-02-25 20:59</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
@@ -8472,25 +8472,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H73" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 19:54</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H73" s="3" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 04:00</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:10</t>
+          <t>2026-03-08 09:08</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
@@ -8499,11 +8499,11 @@
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 02:52</t>
+          <t>2026-03-11 06:42</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
@@ -8512,11 +8512,11 @@
         </is>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:21</t>
+          <t>2026-03-15 14:53</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -8528,13 +8528,13 @@
         <v>25</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>442.8</v>
+        <v>447.9</v>
       </c>
       <c r="V73" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W73" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X73" s="4" t="inlineStr">
         <is>
@@ -8568,86 +8568,86 @@
           <t>فريق 4</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 21:43</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="E74" s="3" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:40</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 00:52</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 08:32</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 06:31</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-16 17:48</t>
+        </is>
+      </c>
+      <c r="S74" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H74" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 16:36</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 03:29</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 18:48</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q74" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="R74" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-18 22:42</t>
-        </is>
-      </c>
-      <c r="S74" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="T74" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>401</v>
+        <v>369.3</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>80.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -8678,11 +8678,11 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>75.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 20:06</t>
+          <t>2026-02-25 09:51</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -8691,11 +8691,11 @@
         </is>
       </c>
       <c r="H75" s="3" t="n">
-        <v>77.3</v>
+        <v>81.8</v>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 19:44</t>
+          <t>2026-03-02 17:28</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -8704,11 +8704,11 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>92.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 18:25</t>
+          <t>2026-03-08 06:05</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -8716,25 +8716,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N75" s="6" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="O75" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 11:57</t>
-        </is>
-      </c>
-      <c r="P75" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N75" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>86.2</v>
+        <v>87.7</v>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 13:41</t>
+          <t>2026-03-15 06:57</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -8743,20 +8743,20 @@
         </is>
       </c>
       <c r="T75" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>376</v>
+        <v>419.7</v>
       </c>
       <c r="V75" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>75.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -8787,11 +8787,11 @@
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>67.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:42</t>
+          <t>2026-02-25 21:04</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -8799,25 +8799,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H76" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 20:00</t>
-        </is>
-      </c>
-      <c r="J76" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H76" s="3" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 04:14</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:19</t>
+          <t>2026-03-08 09:18</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -8826,11 +8826,11 @@
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 03:00</t>
+          <t>2026-03-11 06:44</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -8839,11 +8839,11 @@
         </is>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:32</t>
+          <t>2026-03-15 15:00</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr">
@@ -8855,13 +8855,13 @@
         <v>25</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>442.8</v>
+        <v>447.9</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X76" s="4" t="inlineStr">
         <is>
@@ -8896,11 +8896,11 @@
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>67.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:34</t>
+          <t>2026-02-25 21:14</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -8908,25 +8908,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H77" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 19:59</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H77" s="3" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 04:07</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:14</t>
+          <t>2026-03-08 09:16</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -8935,11 +8935,11 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 02:57</t>
+          <t>2026-03-11 06:50</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
@@ -8948,11 +8948,11 @@
         </is>
       </c>
       <c r="Q77" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:24</t>
+          <t>2026-03-15 15:03</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr">
@@ -8964,13 +8964,13 @@
         <v>25</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>442.8</v>
+        <v>447.9</v>
       </c>
       <c r="V77" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W77" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X77" s="4" t="inlineStr">
         <is>
@@ -9004,25 +9004,25 @@
           <t>فريق 2</t>
         </is>
       </c>
-      <c r="E78" s="3" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 13:15</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E78" s="6" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-25 19:14</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>66.2</v>
+        <v>64</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 20:27</t>
+          <t>2026-03-02 17:48</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
@@ -9030,25 +9030,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="K78" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 03:48</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K78" s="6" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-08 16:50</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>87.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 00:12</t>
+          <t>2026-03-11 10:38</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>78.3</v>
+        <v>83.5</v>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 00:49</t>
+          <t>2026-03-15 09:42</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
@@ -9070,20 +9070,20 @@
         </is>
       </c>
       <c r="T78" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>417.8</v>
+        <v>343.8</v>
       </c>
       <c r="V78" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W78" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
@@ -9113,25 +9113,25 @@
           <t>فريق 2</t>
         </is>
       </c>
-      <c r="E79" s="3" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 13:26</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E79" s="6" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-25 19:24</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>66.2</v>
+        <v>64</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>2026-02-06 20:17</t>
+          <t>2026-03-02 17:47</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
@@ -9139,25 +9139,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="K79" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-19 03:54</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K79" s="6" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-08 16:41</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>87.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 00:03</t>
+          <t>2026-03-11 10:43</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
@@ -9166,11 +9166,11 @@
         </is>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>78.3</v>
+        <v>83.5</v>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 00:56</t>
+          <t>2026-03-15 09:42</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
@@ -9179,20 +9179,20 @@
         </is>
       </c>
       <c r="T79" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>417.8</v>
+        <v>343.8</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -9222,38 +9222,38 @@
           <t>فريق 6</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 22:19</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="E80" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 04:41</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-03 15:48</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H80" s="3" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-06 04:55</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
       <c r="K80" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 04:46</t>
+          <t>2026-03-08 14:56</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -9261,25 +9261,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N80" s="6" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="O80" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-07 13:15</t>
-        </is>
-      </c>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N80" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11 18:49</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>86.5</v>
+        <v>83</v>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 12:05</t>
+          <t>2026-03-15 17:03</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
@@ -9291,13 +9291,13 @@
         <v>0</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>350.6</v>
+        <v>369.1</v>
       </c>
       <c r="V80" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
@@ -9332,11 +9332,11 @@
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>67.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 18:37</t>
+          <t>2026-02-25 21:08</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -9344,25 +9344,25 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H81" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-06 20:00</t>
-        </is>
-      </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H81" s="3" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02 04:01</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 08:12</t>
+          <t>2026-03-08 09:22</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -9371,11 +9371,11 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 02:58</t>
+          <t>2026-03-11 06:48</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
@@ -9384,11 +9384,11 @@
         </is>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 14:23</t>
+          <t>2026-03-15 14:54</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -9400,13 +9400,13 @@
         <v>25</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>442.8</v>
+        <v>447.9</v>
       </c>
       <c r="V81" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W81" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X81" s="4" t="inlineStr">
         <is>
@@ -9441,11 +9441,11 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>63.2</v>
+        <v>73.3</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>2026-01-20 11:09</t>
+          <t>2026-03-08 21:49</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -9454,11 +9454,11 @@
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>69.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 22:12</t>
+          <t>2026-03-10 15:31</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -9509,13 +9509,13 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="n">
-        <v>132.3</v>
+        <v>134.4</v>
       </c>
       <c r="V82" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W82" s="11" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="X82" s="12" t="inlineStr">
         <is>
@@ -9550,11 +9550,11 @@
         </is>
       </c>
       <c r="E83" s="11" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 11:55</t>
+          <t>2026-03-05 17:16</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -9563,11 +9563,11 @@
         </is>
       </c>
       <c r="H83" s="11" t="n">
-        <v>67.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 21:36</t>
+          <t>2026-03-09 16:23</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
@@ -9618,13 +9618,13 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="n">
-        <v>127.8</v>
+        <v>120.8</v>
       </c>
       <c r="V83" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W83" s="11" t="n">
-        <v>25.6</v>
+        <v>24.2</v>
       </c>
       <c r="X83" s="12" t="inlineStr">
         <is>
@@ -9659,11 +9659,11 @@
         </is>
       </c>
       <c r="E84" s="11" t="n">
-        <v>67.40000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22 18:11</t>
+          <t>2026-03-07 18:29</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -9672,11 +9672,11 @@
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>63.1</v>
+        <v>59.1</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>2026-02-07 10:49</t>
+          <t>2026-03-11 17:38</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -9727,13 +9727,13 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="n">
-        <v>130.5</v>
+        <v>119.9</v>
       </c>
       <c r="V84" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W84" s="11" t="n">
-        <v>26.1</v>
+        <v>24</v>
       </c>
       <c r="X84" s="12" t="inlineStr">
         <is>
@@ -9768,11 +9768,11 @@
         </is>
       </c>
       <c r="E85" s="11" t="n">
-        <v>40</v>
+        <v>54.8</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 20:55</t>
+          <t>2026-03-07 16:39</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -9781,11 +9781,11 @@
         </is>
       </c>
       <c r="H85" s="11" t="n">
-        <v>49.1</v>
+        <v>68.7</v>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>2026-02-06 22:20</t>
+          <t>2026-03-10 19:36</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
@@ -9836,13 +9836,13 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>123.5</v>
       </c>
       <c r="V85" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W85" s="11" t="n">
-        <v>17.8</v>
+        <v>24.7</v>
       </c>
       <c r="X85" s="12" t="inlineStr">
         <is>
@@ -9877,11 +9877,11 @@
         </is>
       </c>
       <c r="E86" s="14" t="n">
-        <v>23.2</v>
+        <v>36.4</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 21:42</t>
+          <t>2026-02-25 14:41</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -9890,11 +9890,11 @@
         </is>
       </c>
       <c r="H86" s="14" t="n">
-        <v>25.6</v>
+        <v>44.6</v>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 20:30</t>
+          <t>2026-03-02 21:29</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
@@ -9945,13 +9945,13 @@
         <v>0</v>
       </c>
       <c r="U86" s="11" t="n">
-        <v>48.8</v>
+        <v>81</v>
       </c>
       <c r="V86" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W86" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>16.2</v>
       </c>
       <c r="X86" s="12" t="inlineStr">
         <is>
@@ -9986,11 +9986,11 @@
         </is>
       </c>
       <c r="E87" s="14" t="n">
-        <v>22</v>
+        <v>41.3</v>
       </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
-          <t>2026-01-24 17:54</t>
+          <t>2026-02-25 12:35</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -9999,11 +9999,11 @@
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>41.5</v>
+        <v>28.5</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 18:24</t>
+          <t>2026-03-02 23:59</t>
         </is>
       </c>
       <c r="J87" s="14" t="inlineStr">
@@ -10054,13 +10054,13 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="n">
-        <v>63.5</v>
+        <v>69.8</v>
       </c>
       <c r="V87" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W87" s="11" t="n">
-        <v>12.7</v>
+        <v>14</v>
       </c>
       <c r="X87" s="12" t="inlineStr">
         <is>
@@ -10095,11 +10095,11 @@
         </is>
       </c>
       <c r="E88" s="14" t="n">
-        <v>42.6</v>
+        <v>43.9</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 22:12</t>
+          <t>2026-02-25 19:17</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -10108,11 +10108,11 @@
         </is>
       </c>
       <c r="H88" s="14" t="n">
-        <v>43.8</v>
+        <v>24.8</v>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 19:30</t>
+          <t>2026-03-02 21:05</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
@@ -10163,13 +10163,13 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="n">
-        <v>86.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="V88" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W88" s="11" t="n">
-        <v>17.3</v>
+        <v>13.7</v>
       </c>
       <c r="X88" s="12" t="inlineStr">
         <is>
@@ -10204,11 +10204,11 @@
         </is>
       </c>
       <c r="E89" s="14" t="n">
-        <v>38.3</v>
+        <v>40.8</v>
       </c>
       <c r="F89" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 21:18</t>
+          <t>2026-02-25 18:53</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -10217,11 +10217,11 @@
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>35.9</v>
+        <v>44.4</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 21:54</t>
+          <t>2026-03-02 18:35</t>
         </is>
       </c>
       <c r="J89" s="14" t="inlineStr">
@@ -10272,13 +10272,13 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="n">
-        <v>74.2</v>
+        <v>85.2</v>
       </c>
       <c r="V89" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W89" s="11" t="n">
-        <v>14.8</v>
+        <v>17</v>
       </c>
       <c r="X89" s="12" t="inlineStr">
         <is>
@@ -10313,11 +10313,11 @@
         </is>
       </c>
       <c r="E90" s="11" t="n">
-        <v>63.9</v>
+        <v>66</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>2026-01-20 13:39</t>
+          <t>2026-03-04 18:21</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>70.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 12:41</t>
+          <t>2026-03-05 16:11</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
@@ -10381,13 +10381,13 @@
         <v>0</v>
       </c>
       <c r="U90" s="11" t="n">
-        <v>134.5</v>
+        <v>140.6</v>
       </c>
       <c r="V90" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W90" s="11" t="n">
-        <v>26.9</v>
+        <v>28.1</v>
       </c>
       <c r="X90" s="12" t="inlineStr">
         <is>
@@ -10422,11 +10422,11 @@
         </is>
       </c>
       <c r="E91" s="11" t="n">
-        <v>69.2</v>
+        <v>72.2</v>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 13:11</t>
+          <t>2026-03-04 16:30</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -10435,11 +10435,11 @@
         </is>
       </c>
       <c r="H91" s="11" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 17:06</t>
+          <t>2026-03-03 17:39</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
@@ -10490,13 +10490,13 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="n">
-        <v>145.3</v>
+        <v>147.2</v>
       </c>
       <c r="V91" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W91" s="11" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="X91" s="12" t="inlineStr">
         <is>
@@ -10531,11 +10531,11 @@
         </is>
       </c>
       <c r="E92" s="11" t="n">
-        <v>77</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22 11:11</t>
+          <t>2026-03-08 16:06</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -10544,11 +10544,11 @@
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>78.2</v>
+        <v>75</v>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 09:27</t>
+          <t>2026-03-05 23:08</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
@@ -10599,13 +10599,13 @@
         <v>0</v>
       </c>
       <c r="U92" s="11" t="n">
-        <v>155.2</v>
+        <v>152.6</v>
       </c>
       <c r="V92" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W92" s="11" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="X92" s="12" t="inlineStr">
         <is>
@@ -10640,11 +10640,11 @@
         </is>
       </c>
       <c r="E93" s="11" t="n">
-        <v>70.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>2026-01-20 13:43</t>
+          <t>2026-03-04 20:02</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -10653,11 +10653,11 @@
         </is>
       </c>
       <c r="H93" s="11" t="n">
-        <v>77</v>
+        <v>82.5</v>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 10:04</t>
+          <t>2026-03-05 21:17</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
@@ -10708,13 +10708,13 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="n">
-        <v>147.7</v>
+        <v>154.4</v>
       </c>
       <c r="V93" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W93" s="11" t="n">
-        <v>29.5</v>
+        <v>30.9</v>
       </c>
       <c r="X93" s="12" t="inlineStr">
         <is>
@@ -10748,25 +10748,25 @@
           <t>فريق 4</t>
         </is>
       </c>
-      <c r="E94" s="14" t="n">
-        <v>61</v>
-      </c>
-      <c r="F94" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-23 21:51</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="E94" s="11" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:44</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>74.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 16:30</t>
+          <t>2026-03-02 01:04</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
@@ -10817,13 +10817,13 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="n">
-        <v>135.4</v>
+        <v>149.9</v>
       </c>
       <c r="V94" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W94" s="11" t="n">
-        <v>27.1</v>
+        <v>30</v>
       </c>
       <c r="X94" s="12" t="inlineStr">
         <is>
@@ -10857,25 +10857,25 @@
           <t>فريق 2</t>
         </is>
       </c>
-      <c r="E95" s="11" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-22 13:29</t>
-        </is>
-      </c>
-      <c r="G95" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E95" s="14" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F95" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-25 19:24</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H95" s="14" t="n">
-        <v>66.2</v>
+        <v>64</v>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>2026-02-06 20:19</t>
+          <t>2026-03-02 17:47</t>
         </is>
       </c>
       <c r="J95" s="14" t="inlineStr">
@@ -10926,13 +10926,13 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="n">
-        <v>138.1</v>
+        <v>105.9</v>
       </c>
       <c r="V95" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W95" s="11" t="n">
-        <v>27.6</v>
+        <v>21.2</v>
       </c>
       <c r="X95" s="12" t="inlineStr">
         <is>
@@ -10967,11 +10967,11 @@
         </is>
       </c>
       <c r="E96" s="11" t="n">
-        <v>75.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>2026-01-23 20:00</t>
+          <t>2026-02-25 09:49</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
@@ -10980,11 +10980,11 @@
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>77.3</v>
+        <v>81.8</v>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 19:55</t>
+          <t>2026-03-02 17:40</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
@@ -11035,13 +11035,13 @@
         <v>0</v>
       </c>
       <c r="U96" s="11" t="n">
-        <v>153.1</v>
+        <v>152.4</v>
       </c>
       <c r="V96" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W96" s="11" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="X96" s="12" t="inlineStr">
         <is>
@@ -11076,11 +11076,11 @@
         </is>
       </c>
       <c r="E97" s="14" t="n">
-        <v>60</v>
+        <v>58.2</v>
       </c>
       <c r="F97" s="14" t="inlineStr">
         <is>
-          <t>2026-01-23 22:36</t>
+          <t>2026-02-25 20:10</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -11088,17 +11088,17 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H97" s="14" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="I97" s="14" t="inlineStr">
-        <is>
-          <t>2026-02-06 20:06</t>
-        </is>
-      </c>
-      <c r="J97" s="14" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H97" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-02 12:35</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K97" s="11" t="n">
@@ -11144,13 +11144,13 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="n">
-        <v>123.7</v>
+        <v>131.2</v>
       </c>
       <c r="V97" s="11" t="n">
         <v>500</v>
       </c>
       <c r="W97" s="11" t="n">
-        <v>24.7</v>
+        <v>26.2</v>
       </c>
       <c r="X97" s="12" t="inlineStr">
         <is>
@@ -11271,25 +11271,25 @@
         <v>20</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>67.45</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>72.95</v>
+        <v>69.61</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>64.25</v>
+        <v>63.84</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>65.15000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>62.33</v>
+        <v>66.75</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>335.04</v>
+        <v>336.04</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>67</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>0</v>
@@ -11313,28 +11313,28 @@
         <v>20</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>51.72</v>
+        <v>53.27</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>58.55</v>
+        <v>56.7</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>56.12</v>
+        <v>49.59</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>53.55</v>
+        <v>57.46</v>
       </c>
       <c r="I3" s="19" t="n">
-        <v>51.2</v>
+        <v>57.6</v>
       </c>
       <c r="J3" s="19" t="n">
-        <v>277.18</v>
+        <v>280.66</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>55.44</v>
+        <v>56.13</v>
       </c>
       <c r="L3" s="19" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -11355,25 +11355,25 @@
         <v>20</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>72.45</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>77.06999999999999</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>74.05</v>
+        <v>74.73</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>70.25</v>
+        <v>71.5</v>
       </c>
       <c r="I4" s="20" t="n">
-        <v>69.75</v>
+        <v>70.48</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>372.52</v>
+        <v>375.86</v>
       </c>
       <c r="K4" s="20" t="n">
-        <v>74.51000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="L4" s="20" t="n">
         <v>0</v>
@@ -11397,28 +11397,28 @@
         <v>20</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>66.28</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>70.95</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>75.51000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>59.64</v>
+        <v>68.23</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>70.09999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="J5" s="21" t="n">
-        <v>351.02</v>
+        <v>349.37</v>
       </c>
       <c r="K5" s="21" t="n">
-        <v>70.20999999999999</v>
+        <v>69.88</v>
       </c>
       <c r="L5" s="21" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
